--- a/artfynd/A 31324-2024 artfynd.xlsx
+++ b/artfynd/A 31324-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118676034</v>
+        <v>118676032</v>
       </c>
       <c r="B2" t="n">
-        <v>78220</v>
+        <v>91786</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>477241</v>
+        <v>477240</v>
       </c>
       <c r="R2" t="n">
-        <v>6847418</v>
+        <v>6847421</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118676032</v>
+        <v>118676034</v>
       </c>
       <c r="B3" t="n">
-        <v>91779</v>
+        <v>78227</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,25 +798,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -830,10 +830,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>477240</v>
+        <v>477241</v>
       </c>
       <c r="R3" t="n">
-        <v>6847421</v>
+        <v>6847418</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>

--- a/artfynd/A 31324-2024 artfynd.xlsx
+++ b/artfynd/A 31324-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118676032</v>
+        <v>118676034</v>
       </c>
       <c r="B2" t="n">
-        <v>91786</v>
+        <v>78227</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>477240</v>
+        <v>477241</v>
       </c>
       <c r="R2" t="n">
-        <v>6847421</v>
+        <v>6847418</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118676034</v>
+        <v>118676032</v>
       </c>
       <c r="B3" t="n">
-        <v>78227</v>
+        <v>91786</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,25 +798,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -830,10 +830,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>477241</v>
+        <v>477240</v>
       </c>
       <c r="R3" t="n">
-        <v>6847418</v>
+        <v>6847421</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>

--- a/artfynd/A 31324-2024 artfynd.xlsx
+++ b/artfynd/A 31324-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -895,6 +895,2030 @@
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>123771747</v>
+      </c>
+      <c r="B4" t="n">
+        <v>98396</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Kölsjöhållan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>477134</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6847450</v>
+      </c>
+      <c r="S4" t="n">
+        <v>15</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2024-07-26</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2024-07-26</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Gabriella Fjordmark Lerne</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Gabriella Fjordmark Lerne</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2024 Fågelsjö</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>123771753</v>
+      </c>
+      <c r="B5" t="n">
+        <v>98396</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Kölsjöhållan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>476964</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6847387</v>
+      </c>
+      <c r="S5" t="n">
+        <v>15</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2024-07-26</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2024-07-26</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Blomning över 80 stänglar</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Gabriella Fjordmark Lerne</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Gabriella Fjordmark Lerne</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2024 Fågelsjö</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>123771759</v>
+      </c>
+      <c r="B6" t="n">
+        <v>78781</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Kölsjöhållan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>477096</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6847397</v>
+      </c>
+      <c r="S6" t="n">
+        <v>15</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2024-07-26</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2024-07-26</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Gabriella Fjordmark Lerne</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Gabriella Fjordmark Lerne</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2024 Fågelsjö</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>123771751</v>
+      </c>
+      <c r="B7" t="n">
+        <v>98396</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Kölsjöhållan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>477034</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6847389</v>
+      </c>
+      <c r="S7" t="n">
+        <v>15</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2024-07-26</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2024-07-26</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Gabriella Fjordmark Lerne</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Gabriella Fjordmark Lerne</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2024 Fågelsjö</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>123771752</v>
+      </c>
+      <c r="B8" t="n">
+        <v>98396</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Kölsjöhållan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>477001</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6847417</v>
+      </c>
+      <c r="S8" t="n">
+        <v>15</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2024-07-26</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2024-07-26</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Gabriella Fjordmark Lerne</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Gabriella Fjordmark Lerne</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2024 Fågelsjö</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>123771746</v>
+      </c>
+      <c r="B9" t="n">
+        <v>98396</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Kölsjöhållan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>477174</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6847450</v>
+      </c>
+      <c r="S9" t="n">
+        <v>15</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2024-07-26</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2024-07-26</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Gabriella Fjordmark Lerne</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Gabriella Fjordmark Lerne</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2024 Fågelsjö</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>123771763</v>
+      </c>
+      <c r="B10" t="n">
+        <v>98313</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Kölsjöhållan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>476949</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6847393</v>
+      </c>
+      <c r="S10" t="n">
+        <v>15</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2024-07-26</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2024-07-26</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Gabriella Fjordmark Lerne</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Gabriella Fjordmark Lerne</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2024 Fågelsjö</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>123771760</v>
+      </c>
+      <c r="B11" t="n">
+        <v>78781</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Kölsjöhållan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>477028</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6847394</v>
+      </c>
+      <c r="S11" t="n">
+        <v>15</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2024-07-26</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2024-07-26</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Gabriella Fjordmark Lerne</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Gabriella Fjordmark Lerne</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2024 Fågelsjö</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>123771756</v>
+      </c>
+      <c r="B12" t="n">
+        <v>98396</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Kölsjöhållan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>476937</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6847291</v>
+      </c>
+      <c r="S12" t="n">
+        <v>15</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2024-07-26</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2024-07-26</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Minst 100 många i blom</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Gabriella Fjordmark Lerne</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Gabriella Fjordmark Lerne</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2024 Fågelsjö</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>123771757</v>
+      </c>
+      <c r="B13" t="n">
+        <v>98396</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Kölsjöhållan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>476911</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6847329</v>
+      </c>
+      <c r="S13" t="n">
+        <v>15</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2024-07-26</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2024-07-26</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Gabriella Fjordmark Lerne</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Gabriella Fjordmark Lerne</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2024 Fågelsjö</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>123771749</v>
+      </c>
+      <c r="B14" t="n">
+        <v>98396</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Kölsjöhållan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>477122</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6847410</v>
+      </c>
+      <c r="S14" t="n">
+        <v>15</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2024-07-26</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2024-07-26</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Gabriella Fjordmark Lerne</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Gabriella Fjordmark Lerne</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2024 Fågelsjö</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>123771750</v>
+      </c>
+      <c r="B15" t="n">
+        <v>98396</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Kölsjöhållan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>477093</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6847398</v>
+      </c>
+      <c r="S15" t="n">
+        <v>15</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2024-07-26</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2024-07-26</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Gabriella Fjordmark Lerne</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Gabriella Fjordmark Lerne</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2024 Fågelsjö</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>123771732</v>
+      </c>
+      <c r="B16" t="n">
+        <v>79890</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>6461</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Norrlandslav</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Nephroma arcticum</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(L.) Torss.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Kölsjöhållan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>477018</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6847382</v>
+      </c>
+      <c r="S16" t="n">
+        <v>15</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2024-07-26</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2024-07-26</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Gabriella Fjordmark Lerne</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Gabriella Fjordmark Lerne</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2024 Fågelsjö</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>123771748</v>
+      </c>
+      <c r="B17" t="n">
+        <v>98396</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Kölsjöhållan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>477135</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6847443</v>
+      </c>
+      <c r="S17" t="n">
+        <v>15</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2024-07-26</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2024-07-26</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Gabriella Fjordmark Lerne</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Gabriella Fjordmark Lerne</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2024 Fågelsjö</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>123771718</v>
+      </c>
+      <c r="B18" t="n">
+        <v>79399</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Kölsjöhållan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>477293</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6847591</v>
+      </c>
+      <c r="S18" t="n">
+        <v>15</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2024-07-26</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2024-07-26</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Gabriella Fjordmark Lerne</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Gabriella Fjordmark Lerne</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2024 Fågelsjö</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>123771744</v>
+      </c>
+      <c r="B19" t="n">
+        <v>98396</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Kölsjöhållan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>477281</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6847618</v>
+      </c>
+      <c r="S19" t="n">
+        <v>15</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2024-07-26</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2024-07-26</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Gabriella Fjordmark Lerne</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Gabriella Fjordmark Lerne</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2024 Fågelsjö</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>123771745</v>
+      </c>
+      <c r="B20" t="n">
+        <v>98396</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Kölsjöhållan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>477255</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6847445</v>
+      </c>
+      <c r="S20" t="n">
+        <v>15</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2024-07-26</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2024-07-26</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Gabriella Fjordmark Lerne</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Gabriella Fjordmark Lerne</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2024 Fågelsjö</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>123771754</v>
+      </c>
+      <c r="B21" t="n">
+        <v>98396</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Kölsjöhållan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>476918</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6847369</v>
+      </c>
+      <c r="S21" t="n">
+        <v>15</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2024-07-26</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2024-07-26</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Gabriella Fjordmark Lerne</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Gabriella Fjordmark Lerne</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2024 Fågelsjö</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>123771733</v>
+      </c>
+      <c r="B22" t="n">
+        <v>78518</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Kölsjöhållan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>477300</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6847594</v>
+      </c>
+      <c r="S22" t="n">
+        <v>15</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2024-07-26</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2024-07-26</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Gabriella Fjordmark Lerne</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Gabriella Fjordmark Lerne</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2024 Fågelsjö</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 31324-2024 artfynd.xlsx
+++ b/artfynd/A 31324-2024 artfynd.xlsx
@@ -2709,10 +2709,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123771754</v>
+        <v>123771733</v>
       </c>
       <c r="B21" t="n">
-        <v>98396</v>
+        <v>78518</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2721,25 +2721,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2749,10 +2749,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>476918</v>
+        <v>477300</v>
       </c>
       <c r="R21" t="n">
-        <v>6847369</v>
+        <v>6847594</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2815,10 +2815,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123771733</v>
+        <v>123771754</v>
       </c>
       <c r="B22" t="n">
-        <v>78518</v>
+        <v>98396</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2827,25 +2827,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2855,10 +2855,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>477300</v>
+        <v>476918</v>
       </c>
       <c r="R22" t="n">
-        <v>6847594</v>
+        <v>6847369</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>

--- a/artfynd/A 31324-2024 artfynd.xlsx
+++ b/artfynd/A 31324-2024 artfynd.xlsx
@@ -897,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123771747</v>
+        <v>123771718</v>
       </c>
       <c r="B4" t="n">
-        <v>98396</v>
+        <v>79404</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -909,25 +909,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -937,10 +937,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>477134</v>
+        <v>477293</v>
       </c>
       <c r="R4" t="n">
-        <v>6847450</v>
+        <v>6847591</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -1003,10 +1003,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123771753</v>
+        <v>123771754</v>
       </c>
       <c r="B5" t="n">
-        <v>98396</v>
+        <v>98502</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1043,10 +1043,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>476964</v>
+        <v>476918</v>
       </c>
       <c r="R5" t="n">
-        <v>6847387</v>
+        <v>6847369</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1079,11 +1079,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-07-26</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Blomning över 80 stänglar</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1114,10 +1109,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123771759</v>
+        <v>123771748</v>
       </c>
       <c r="B6" t="n">
-        <v>78781</v>
+        <v>98502</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1126,25 +1121,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1154,10 +1149,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>477096</v>
+        <v>477135</v>
       </c>
       <c r="R6" t="n">
-        <v>6847397</v>
+        <v>6847443</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1220,10 +1215,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123771751</v>
+        <v>123771746</v>
       </c>
       <c r="B7" t="n">
-        <v>98396</v>
+        <v>98502</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1260,10 +1255,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>477034</v>
+        <v>477174</v>
       </c>
       <c r="R7" t="n">
-        <v>6847389</v>
+        <v>6847450</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1326,10 +1321,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123771752</v>
+        <v>123771753</v>
       </c>
       <c r="B8" t="n">
-        <v>98396</v>
+        <v>98502</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1366,10 +1361,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>477001</v>
+        <v>476964</v>
       </c>
       <c r="R8" t="n">
-        <v>6847417</v>
+        <v>6847387</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1402,6 +1397,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2024-07-26</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Blomning över 80 stänglar</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1432,10 +1432,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123771746</v>
+        <v>123771749</v>
       </c>
       <c r="B9" t="n">
-        <v>98396</v>
+        <v>98502</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1472,10 +1472,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>477174</v>
+        <v>477122</v>
       </c>
       <c r="R9" t="n">
-        <v>6847450</v>
+        <v>6847410</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1538,10 +1538,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123771763</v>
+        <v>123771751</v>
       </c>
       <c r="B10" t="n">
-        <v>98313</v>
+        <v>98502</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1550,25 +1550,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>219790</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1578,10 +1578,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>476949</v>
+        <v>477034</v>
       </c>
       <c r="R10" t="n">
-        <v>6847393</v>
+        <v>6847389</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1644,10 +1644,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123771760</v>
+        <v>123771752</v>
       </c>
       <c r="B11" t="n">
-        <v>78781</v>
+        <v>98502</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1656,25 +1656,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1684,10 +1684,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>477028</v>
+        <v>477001</v>
       </c>
       <c r="R11" t="n">
-        <v>6847394</v>
+        <v>6847417</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1750,10 +1750,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123771756</v>
+        <v>123771732</v>
       </c>
       <c r="B12" t="n">
-        <v>98396</v>
+        <v>79895</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1762,25 +1762,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>6461</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1790,10 +1790,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>476937</v>
+        <v>477018</v>
       </c>
       <c r="R12" t="n">
-        <v>6847291</v>
+        <v>6847382</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1826,11 +1826,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2024-07-26</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Minst 100 många i blom</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1861,10 +1856,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123771757</v>
+        <v>123771750</v>
       </c>
       <c r="B13" t="n">
-        <v>98396</v>
+        <v>98502</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1901,10 +1896,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>476911</v>
+        <v>477093</v>
       </c>
       <c r="R13" t="n">
-        <v>6847329</v>
+        <v>6847398</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1967,10 +1962,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123771749</v>
+        <v>123771757</v>
       </c>
       <c r="B14" t="n">
-        <v>98396</v>
+        <v>98502</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2007,10 +2002,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>477122</v>
+        <v>476911</v>
       </c>
       <c r="R14" t="n">
-        <v>6847410</v>
+        <v>6847329</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2073,10 +2068,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123771750</v>
+        <v>123771744</v>
       </c>
       <c r="B15" t="n">
-        <v>98396</v>
+        <v>98502</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2113,10 +2108,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>477093</v>
+        <v>477281</v>
       </c>
       <c r="R15" t="n">
-        <v>6847398</v>
+        <v>6847618</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2179,10 +2174,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123771732</v>
+        <v>123771763</v>
       </c>
       <c r="B16" t="n">
-        <v>79890</v>
+        <v>98419</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2195,21 +2190,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6461</v>
+        <v>219790</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2219,10 +2214,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>477018</v>
+        <v>476949</v>
       </c>
       <c r="R16" t="n">
-        <v>6847382</v>
+        <v>6847393</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2285,10 +2280,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123771748</v>
+        <v>123771759</v>
       </c>
       <c r="B17" t="n">
-        <v>98396</v>
+        <v>78786</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2297,25 +2292,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2325,10 +2320,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>477135</v>
+        <v>477096</v>
       </c>
       <c r="R17" t="n">
-        <v>6847443</v>
+        <v>6847397</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2391,10 +2386,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123771718</v>
+        <v>123771745</v>
       </c>
       <c r="B18" t="n">
-        <v>79399</v>
+        <v>98502</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2403,25 +2398,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2431,10 +2426,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>477293</v>
+        <v>477255</v>
       </c>
       <c r="R18" t="n">
-        <v>6847591</v>
+        <v>6847445</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2497,10 +2492,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123771744</v>
+        <v>123771756</v>
       </c>
       <c r="B19" t="n">
-        <v>98396</v>
+        <v>98502</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2537,10 +2532,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>477281</v>
+        <v>476937</v>
       </c>
       <c r="R19" t="n">
-        <v>6847618</v>
+        <v>6847291</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2573,6 +2568,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2024-07-26</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Minst 100 många i blom</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2603,10 +2603,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123771745</v>
+        <v>123771760</v>
       </c>
       <c r="B20" t="n">
-        <v>98396</v>
+        <v>78786</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2615,25 +2615,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2643,10 +2643,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>477255</v>
+        <v>477028</v>
       </c>
       <c r="R20" t="n">
-        <v>6847445</v>
+        <v>6847394</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2709,10 +2709,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123771733</v>
+        <v>123771747</v>
       </c>
       <c r="B21" t="n">
-        <v>78518</v>
+        <v>98502</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2721,25 +2721,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2749,10 +2749,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>477300</v>
+        <v>477134</v>
       </c>
       <c r="R21" t="n">
-        <v>6847594</v>
+        <v>6847450</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2815,10 +2815,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123771754</v>
+        <v>123771733</v>
       </c>
       <c r="B22" t="n">
-        <v>98396</v>
+        <v>78523</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2827,25 +2827,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2855,10 +2855,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>476918</v>
+        <v>477300</v>
       </c>
       <c r="R22" t="n">
-        <v>6847369</v>
+        <v>6847594</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>

--- a/artfynd/A 31324-2024 artfynd.xlsx
+++ b/artfynd/A 31324-2024 artfynd.xlsx
@@ -897,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123771718</v>
+        <v>123771750</v>
       </c>
       <c r="B4" t="n">
-        <v>79404</v>
+        <v>98504</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -909,25 +909,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -937,10 +937,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>477293</v>
+        <v>477093</v>
       </c>
       <c r="R4" t="n">
-        <v>6847591</v>
+        <v>6847398</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -1003,10 +1003,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123771754</v>
+        <v>123771748</v>
       </c>
       <c r="B5" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1043,10 +1043,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>476918</v>
+        <v>477135</v>
       </c>
       <c r="R5" t="n">
-        <v>6847369</v>
+        <v>6847443</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1109,10 +1109,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123771748</v>
+        <v>123771718</v>
       </c>
       <c r="B6" t="n">
-        <v>98502</v>
+        <v>79406</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1121,25 +1121,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1149,10 +1149,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>477135</v>
+        <v>477293</v>
       </c>
       <c r="R6" t="n">
-        <v>6847443</v>
+        <v>6847591</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1215,10 +1215,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123771746</v>
+        <v>123771763</v>
       </c>
       <c r="B7" t="n">
-        <v>98502</v>
+        <v>98421</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1227,25 +1227,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1255,10 +1255,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>477174</v>
+        <v>476949</v>
       </c>
       <c r="R7" t="n">
-        <v>6847450</v>
+        <v>6847393</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1324,7 +1324,7 @@
         <v>123771753</v>
       </c>
       <c r="B8" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1432,10 +1432,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123771749</v>
+        <v>123771751</v>
       </c>
       <c r="B9" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1472,10 +1472,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>477122</v>
+        <v>477034</v>
       </c>
       <c r="R9" t="n">
-        <v>6847410</v>
+        <v>6847389</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1538,10 +1538,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123771751</v>
+        <v>123771757</v>
       </c>
       <c r="B10" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1578,10 +1578,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>477034</v>
+        <v>476911</v>
       </c>
       <c r="R10" t="n">
-        <v>6847389</v>
+        <v>6847329</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1644,10 +1644,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123771752</v>
+        <v>123771732</v>
       </c>
       <c r="B11" t="n">
-        <v>98502</v>
+        <v>79897</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1656,25 +1656,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>6461</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1684,10 +1684,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>477001</v>
+        <v>477018</v>
       </c>
       <c r="R11" t="n">
-        <v>6847417</v>
+        <v>6847382</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1750,10 +1750,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123771732</v>
+        <v>123771747</v>
       </c>
       <c r="B12" t="n">
-        <v>79895</v>
+        <v>98504</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1762,25 +1762,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6461</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1790,10 +1790,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>477018</v>
+        <v>477134</v>
       </c>
       <c r="R12" t="n">
-        <v>6847382</v>
+        <v>6847450</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1856,10 +1856,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123771750</v>
+        <v>123771733</v>
       </c>
       <c r="B13" t="n">
-        <v>98502</v>
+        <v>78525</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1868,25 +1868,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1896,10 +1896,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>477093</v>
+        <v>477300</v>
       </c>
       <c r="R13" t="n">
-        <v>6847398</v>
+        <v>6847594</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1962,10 +1962,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123771757</v>
+        <v>123771746</v>
       </c>
       <c r="B14" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2002,10 +2002,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>476911</v>
+        <v>477174</v>
       </c>
       <c r="R14" t="n">
-        <v>6847329</v>
+        <v>6847450</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2068,10 +2068,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123771744</v>
+        <v>123771760</v>
       </c>
       <c r="B15" t="n">
-        <v>98502</v>
+        <v>78788</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2080,25 +2080,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2108,10 +2108,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>477281</v>
+        <v>477028</v>
       </c>
       <c r="R15" t="n">
-        <v>6847618</v>
+        <v>6847394</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2174,10 +2174,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123771763</v>
+        <v>123771754</v>
       </c>
       <c r="B16" t="n">
-        <v>98419</v>
+        <v>98504</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2186,25 +2186,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>219790</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2214,10 +2214,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>476949</v>
+        <v>476918</v>
       </c>
       <c r="R16" t="n">
-        <v>6847393</v>
+        <v>6847369</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2280,10 +2280,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123771759</v>
+        <v>123771744</v>
       </c>
       <c r="B17" t="n">
-        <v>78786</v>
+        <v>98504</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2292,25 +2292,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2320,10 +2320,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>477096</v>
+        <v>477281</v>
       </c>
       <c r="R17" t="n">
-        <v>6847397</v>
+        <v>6847618</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2386,10 +2386,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123771745</v>
+        <v>123771749</v>
       </c>
       <c r="B18" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2426,10 +2426,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>477255</v>
+        <v>477122</v>
       </c>
       <c r="R18" t="n">
-        <v>6847445</v>
+        <v>6847410</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2492,10 +2492,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123771756</v>
+        <v>123771759</v>
       </c>
       <c r="B19" t="n">
-        <v>98502</v>
+        <v>78788</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2504,25 +2504,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2532,10 +2532,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>476937</v>
+        <v>477096</v>
       </c>
       <c r="R19" t="n">
-        <v>6847291</v>
+        <v>6847397</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2568,11 +2568,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2024-07-26</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Minst 100 många i blom</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2603,10 +2598,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123771760</v>
+        <v>123771752</v>
       </c>
       <c r="B20" t="n">
-        <v>78786</v>
+        <v>98504</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2615,25 +2610,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2643,10 +2638,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>477028</v>
+        <v>477001</v>
       </c>
       <c r="R20" t="n">
-        <v>6847394</v>
+        <v>6847417</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2709,10 +2704,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123771747</v>
+        <v>123771745</v>
       </c>
       <c r="B21" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2749,10 +2744,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>477134</v>
+        <v>477255</v>
       </c>
       <c r="R21" t="n">
-        <v>6847450</v>
+        <v>6847445</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2815,10 +2810,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123771733</v>
+        <v>123771756</v>
       </c>
       <c r="B22" t="n">
-        <v>78523</v>
+        <v>98504</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2827,25 +2822,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2855,10 +2850,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>477300</v>
+        <v>476937</v>
       </c>
       <c r="R22" t="n">
-        <v>6847594</v>
+        <v>6847291</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2891,6 +2886,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2024-07-26</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Minst 100 många i blom</t>
         </is>
       </c>
       <c r="AD22" t="b">

--- a/artfynd/A 31324-2024 artfynd.xlsx
+++ b/artfynd/A 31324-2024 artfynd.xlsx
@@ -1750,10 +1750,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123771747</v>
+        <v>123771733</v>
       </c>
       <c r="B12" t="n">
-        <v>98504</v>
+        <v>78525</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1762,25 +1762,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1790,10 +1790,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>477134</v>
+        <v>477300</v>
       </c>
       <c r="R12" t="n">
-        <v>6847450</v>
+        <v>6847594</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1856,10 +1856,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123771733</v>
+        <v>123771747</v>
       </c>
       <c r="B13" t="n">
-        <v>78525</v>
+        <v>98504</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1868,25 +1868,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1896,10 +1896,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>477300</v>
+        <v>477134</v>
       </c>
       <c r="R13" t="n">
-        <v>6847594</v>
+        <v>6847450</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1962,10 +1962,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123771746</v>
+        <v>123771760</v>
       </c>
       <c r="B14" t="n">
-        <v>98504</v>
+        <v>78788</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1974,25 +1974,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2002,10 +2002,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>477174</v>
+        <v>477028</v>
       </c>
       <c r="R14" t="n">
-        <v>6847450</v>
+        <v>6847394</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2068,10 +2068,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123771760</v>
+        <v>123771746</v>
       </c>
       <c r="B15" t="n">
-        <v>78788</v>
+        <v>98504</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2080,25 +2080,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2108,10 +2108,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>477028</v>
+        <v>477174</v>
       </c>
       <c r="R15" t="n">
-        <v>6847394</v>
+        <v>6847450</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>

--- a/artfynd/A 31324-2024 artfynd.xlsx
+++ b/artfynd/A 31324-2024 artfynd.xlsx
@@ -897,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123771750</v>
+        <v>123771763</v>
       </c>
       <c r="B4" t="n">
-        <v>98504</v>
+        <v>97996</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -909,25 +909,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -937,10 +937,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>477093</v>
+        <v>476949</v>
       </c>
       <c r="R4" t="n">
-        <v>6847398</v>
+        <v>6847393</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -1003,10 +1003,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123771748</v>
+        <v>123771733</v>
       </c>
       <c r="B5" t="n">
-        <v>98504</v>
+        <v>78525</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1015,25 +1015,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1043,10 +1043,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>477135</v>
+        <v>477300</v>
       </c>
       <c r="R5" t="n">
-        <v>6847443</v>
+        <v>6847594</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1109,10 +1109,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123771718</v>
+        <v>123771744</v>
       </c>
       <c r="B6" t="n">
-        <v>79406</v>
+        <v>98079</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1121,25 +1121,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1149,10 +1149,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>477293</v>
+        <v>477281</v>
       </c>
       <c r="R6" t="n">
-        <v>6847591</v>
+        <v>6847618</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1215,10 +1215,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123771763</v>
+        <v>123771748</v>
       </c>
       <c r="B7" t="n">
-        <v>98421</v>
+        <v>98079</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1227,25 +1227,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>219790</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1255,10 +1255,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>476949</v>
+        <v>477135</v>
       </c>
       <c r="R7" t="n">
-        <v>6847393</v>
+        <v>6847443</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1321,10 +1321,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123771753</v>
+        <v>123771757</v>
       </c>
       <c r="B8" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1361,10 +1361,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>476964</v>
+        <v>476911</v>
       </c>
       <c r="R8" t="n">
-        <v>6847387</v>
+        <v>6847329</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1397,11 +1397,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2024-07-26</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Blomning över 80 stänglar</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1432,10 +1427,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123771751</v>
+        <v>123771750</v>
       </c>
       <c r="B9" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1472,10 +1467,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>477034</v>
+        <v>477093</v>
       </c>
       <c r="R9" t="n">
-        <v>6847389</v>
+        <v>6847398</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1538,10 +1533,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123771757</v>
+        <v>123771746</v>
       </c>
       <c r="B10" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1578,10 +1573,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>476911</v>
+        <v>477174</v>
       </c>
       <c r="R10" t="n">
-        <v>6847329</v>
+        <v>6847450</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1644,10 +1639,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123771732</v>
+        <v>123771749</v>
       </c>
       <c r="B11" t="n">
-        <v>79897</v>
+        <v>98079</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1656,25 +1651,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6461</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1684,10 +1679,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>477018</v>
+        <v>477122</v>
       </c>
       <c r="R11" t="n">
-        <v>6847382</v>
+        <v>6847410</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1750,10 +1745,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123771733</v>
+        <v>123771759</v>
       </c>
       <c r="B12" t="n">
-        <v>78525</v>
+        <v>78788</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1766,21 +1761,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1790,10 +1785,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>477300</v>
+        <v>477096</v>
       </c>
       <c r="R12" t="n">
-        <v>6847594</v>
+        <v>6847397</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1856,10 +1851,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123771747</v>
+        <v>123771745</v>
       </c>
       <c r="B13" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1896,10 +1891,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>477134</v>
+        <v>477255</v>
       </c>
       <c r="R13" t="n">
-        <v>6847450</v>
+        <v>6847445</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1962,10 +1957,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123771760</v>
+        <v>123771747</v>
       </c>
       <c r="B14" t="n">
-        <v>78788</v>
+        <v>98079</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1974,25 +1969,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2002,10 +1997,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>477028</v>
+        <v>477134</v>
       </c>
       <c r="R14" t="n">
-        <v>6847394</v>
+        <v>6847450</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2068,10 +2063,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123771746</v>
+        <v>123771752</v>
       </c>
       <c r="B15" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2108,10 +2103,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>477174</v>
+        <v>477001</v>
       </c>
       <c r="R15" t="n">
-        <v>6847450</v>
+        <v>6847417</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2177,7 +2172,7 @@
         <v>123771754</v>
       </c>
       <c r="B16" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2280,10 +2275,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123771744</v>
+        <v>123771718</v>
       </c>
       <c r="B17" t="n">
-        <v>98504</v>
+        <v>79406</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2292,25 +2287,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2320,10 +2315,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>477281</v>
+        <v>477293</v>
       </c>
       <c r="R17" t="n">
-        <v>6847618</v>
+        <v>6847591</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2386,10 +2381,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123771749</v>
+        <v>123771751</v>
       </c>
       <c r="B18" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2426,10 +2421,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>477122</v>
+        <v>477034</v>
       </c>
       <c r="R18" t="n">
-        <v>6847410</v>
+        <v>6847389</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2492,10 +2487,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123771759</v>
+        <v>123771753</v>
       </c>
       <c r="B19" t="n">
-        <v>78788</v>
+        <v>98079</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2504,25 +2499,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2532,10 +2527,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>477096</v>
+        <v>476964</v>
       </c>
       <c r="R19" t="n">
-        <v>6847397</v>
+        <v>6847387</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2568,6 +2563,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2024-07-26</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Blomning över 80 stänglar</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2598,10 +2598,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123771752</v>
+        <v>123771760</v>
       </c>
       <c r="B20" t="n">
-        <v>98504</v>
+        <v>78788</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2610,25 +2610,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2638,10 +2638,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>477001</v>
+        <v>477028</v>
       </c>
       <c r="R20" t="n">
-        <v>6847417</v>
+        <v>6847394</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2704,10 +2704,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123771745</v>
+        <v>123771732</v>
       </c>
       <c r="B21" t="n">
-        <v>98504</v>
+        <v>79897</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2716,25 +2716,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>6461</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2744,10 +2744,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>477255</v>
+        <v>477018</v>
       </c>
       <c r="R21" t="n">
-        <v>6847445</v>
+        <v>6847382</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2813,7 +2813,7 @@
         <v>123771756</v>
       </c>
       <c r="B22" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>

--- a/artfynd/A 31324-2024 artfynd.xlsx
+++ b/artfynd/A 31324-2024 artfynd.xlsx
@@ -2704,10 +2704,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123771732</v>
+        <v>123771756</v>
       </c>
       <c r="B21" t="n">
-        <v>79897</v>
+        <v>98079</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2716,25 +2716,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6461</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2744,10 +2744,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>477018</v>
+        <v>476937</v>
       </c>
       <c r="R21" t="n">
-        <v>6847382</v>
+        <v>6847291</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2780,6 +2780,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2024-07-26</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Minst 100 många i blom</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2810,10 +2815,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123771756</v>
+        <v>123771732</v>
       </c>
       <c r="B22" t="n">
-        <v>98079</v>
+        <v>79897</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2822,25 +2827,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>6461</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2850,10 +2855,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>476937</v>
+        <v>477018</v>
       </c>
       <c r="R22" t="n">
-        <v>6847291</v>
+        <v>6847382</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2886,11 +2891,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2024-07-26</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Minst 100 många i blom</t>
         </is>
       </c>
       <c r="AD22" t="b">

--- a/artfynd/A 31324-2024 artfynd.xlsx
+++ b/artfynd/A 31324-2024 artfynd.xlsx
@@ -1003,10 +1003,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123771733</v>
+        <v>123771753</v>
       </c>
       <c r="B5" t="n">
-        <v>78525</v>
+        <v>98079</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1015,25 +1015,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1043,10 +1043,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>477300</v>
+        <v>476964</v>
       </c>
       <c r="R5" t="n">
-        <v>6847594</v>
+        <v>6847387</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1079,6 +1079,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-07-26</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Blomning över 80 stänglar</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1109,7 +1114,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123771744</v>
+        <v>123771751</v>
       </c>
       <c r="B6" t="n">
         <v>98079</v>
@@ -1149,10 +1154,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>477281</v>
+        <v>477034</v>
       </c>
       <c r="R6" t="n">
-        <v>6847618</v>
+        <v>6847389</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1215,7 +1220,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123771748</v>
+        <v>123771745</v>
       </c>
       <c r="B7" t="n">
         <v>98079</v>
@@ -1255,10 +1260,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>477135</v>
+        <v>477255</v>
       </c>
       <c r="R7" t="n">
-        <v>6847443</v>
+        <v>6847445</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1321,7 +1326,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123771757</v>
+        <v>123771747</v>
       </c>
       <c r="B8" t="n">
         <v>98079</v>
@@ -1361,10 +1366,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>476911</v>
+        <v>477134</v>
       </c>
       <c r="R8" t="n">
-        <v>6847329</v>
+        <v>6847450</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1427,10 +1432,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123771750</v>
+        <v>123771760</v>
       </c>
       <c r="B9" t="n">
-        <v>98079</v>
+        <v>78788</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1439,25 +1444,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1467,10 +1472,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>477093</v>
+        <v>477028</v>
       </c>
       <c r="R9" t="n">
-        <v>6847398</v>
+        <v>6847394</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1533,7 +1538,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123771746</v>
+        <v>123771757</v>
       </c>
       <c r="B10" t="n">
         <v>98079</v>
@@ -1573,10 +1578,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>477174</v>
+        <v>476911</v>
       </c>
       <c r="R10" t="n">
-        <v>6847450</v>
+        <v>6847329</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1639,10 +1644,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123771749</v>
+        <v>123771718</v>
       </c>
       <c r="B11" t="n">
-        <v>98079</v>
+        <v>79406</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1651,25 +1656,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1679,10 +1684,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>477122</v>
+        <v>477293</v>
       </c>
       <c r="R11" t="n">
-        <v>6847410</v>
+        <v>6847591</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1745,10 +1750,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123771759</v>
+        <v>123771750</v>
       </c>
       <c r="B12" t="n">
-        <v>78788</v>
+        <v>98079</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1757,25 +1762,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1785,10 +1790,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>477096</v>
+        <v>477093</v>
       </c>
       <c r="R12" t="n">
-        <v>6847397</v>
+        <v>6847398</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1851,10 +1856,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123771745</v>
+        <v>123771759</v>
       </c>
       <c r="B13" t="n">
-        <v>98079</v>
+        <v>78788</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1863,25 +1868,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1891,10 +1896,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>477255</v>
+        <v>477096</v>
       </c>
       <c r="R13" t="n">
-        <v>6847445</v>
+        <v>6847397</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1957,7 +1962,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123771747</v>
+        <v>123771748</v>
       </c>
       <c r="B14" t="n">
         <v>98079</v>
@@ -1997,10 +2002,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>477134</v>
+        <v>477135</v>
       </c>
       <c r="R14" t="n">
-        <v>6847450</v>
+        <v>6847443</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2063,7 +2068,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123771752</v>
+        <v>123771744</v>
       </c>
       <c r="B15" t="n">
         <v>98079</v>
@@ -2103,10 +2108,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>477001</v>
+        <v>477281</v>
       </c>
       <c r="R15" t="n">
-        <v>6847417</v>
+        <v>6847618</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2169,7 +2174,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123771754</v>
+        <v>123771746</v>
       </c>
       <c r="B16" t="n">
         <v>98079</v>
@@ -2209,10 +2214,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>476918</v>
+        <v>477174</v>
       </c>
       <c r="R16" t="n">
-        <v>6847369</v>
+        <v>6847450</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2275,10 +2280,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123771718</v>
+        <v>123771733</v>
       </c>
       <c r="B17" t="n">
-        <v>79406</v>
+        <v>78525</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2291,21 +2296,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2315,10 +2320,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>477293</v>
+        <v>477300</v>
       </c>
       <c r="R17" t="n">
-        <v>6847591</v>
+        <v>6847594</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2381,7 +2386,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123771751</v>
+        <v>123771749</v>
       </c>
       <c r="B18" t="n">
         <v>98079</v>
@@ -2421,10 +2426,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>477034</v>
+        <v>477122</v>
       </c>
       <c r="R18" t="n">
-        <v>6847389</v>
+        <v>6847410</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2487,7 +2492,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123771753</v>
+        <v>123771756</v>
       </c>
       <c r="B19" t="n">
         <v>98079</v>
@@ -2527,10 +2532,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>476964</v>
+        <v>476937</v>
       </c>
       <c r="R19" t="n">
-        <v>6847387</v>
+        <v>6847291</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2567,7 +2572,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Blomning över 80 stänglar</t>
+          <t>Minst 100 många i blom</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2598,10 +2603,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123771760</v>
+        <v>123771732</v>
       </c>
       <c r="B20" t="n">
-        <v>78788</v>
+        <v>79897</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2610,25 +2615,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>6461</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2638,10 +2643,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>477028</v>
+        <v>477018</v>
       </c>
       <c r="R20" t="n">
-        <v>6847394</v>
+        <v>6847382</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2704,7 +2709,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123771756</v>
+        <v>123771754</v>
       </c>
       <c r="B21" t="n">
         <v>98079</v>
@@ -2744,10 +2749,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>476937</v>
+        <v>476918</v>
       </c>
       <c r="R21" t="n">
-        <v>6847291</v>
+        <v>6847369</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2780,11 +2785,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2024-07-26</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Minst 100 många i blom</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2815,10 +2815,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123771732</v>
+        <v>123771752</v>
       </c>
       <c r="B22" t="n">
-        <v>79897</v>
+        <v>98079</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2827,25 +2827,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6461</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2855,10 +2855,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>477018</v>
+        <v>477001</v>
       </c>
       <c r="R22" t="n">
-        <v>6847382</v>
+        <v>6847417</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>

--- a/artfynd/A 31324-2024 artfynd.xlsx
+++ b/artfynd/A 31324-2024 artfynd.xlsx
@@ -897,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123771763</v>
+        <v>123771753</v>
       </c>
       <c r="B4" t="n">
-        <v>97996</v>
+        <v>98079</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -909,25 +909,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>219790</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -937,10 +937,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>476949</v>
+        <v>476964</v>
       </c>
       <c r="R4" t="n">
-        <v>6847393</v>
+        <v>6847387</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -973,6 +973,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-07-26</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Blomning över 80 stänglar</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1003,7 +1008,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123771753</v>
+        <v>123771752</v>
       </c>
       <c r="B5" t="n">
         <v>98079</v>
@@ -1043,10 +1048,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>476964</v>
+        <v>477001</v>
       </c>
       <c r="R5" t="n">
-        <v>6847387</v>
+        <v>6847417</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1079,11 +1084,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-07-26</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Blomning över 80 stänglar</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1114,10 +1114,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123771751</v>
+        <v>123771759</v>
       </c>
       <c r="B6" t="n">
-        <v>98079</v>
+        <v>78788</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1126,25 +1126,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1154,10 +1154,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>477034</v>
+        <v>477096</v>
       </c>
       <c r="R6" t="n">
-        <v>6847389</v>
+        <v>6847397</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1220,7 +1220,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123771745</v>
+        <v>123771757</v>
       </c>
       <c r="B7" t="n">
         <v>98079</v>
@@ -1260,10 +1260,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>477255</v>
+        <v>476911</v>
       </c>
       <c r="R7" t="n">
-        <v>6847445</v>
+        <v>6847329</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1326,10 +1326,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123771747</v>
+        <v>123771732</v>
       </c>
       <c r="B8" t="n">
-        <v>98079</v>
+        <v>79897</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1338,25 +1338,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>6461</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1366,10 +1366,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>477134</v>
+        <v>477018</v>
       </c>
       <c r="R8" t="n">
-        <v>6847450</v>
+        <v>6847382</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1432,10 +1432,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123771760</v>
+        <v>123771751</v>
       </c>
       <c r="B9" t="n">
-        <v>78788</v>
+        <v>98079</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1444,25 +1444,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1472,10 +1472,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>477028</v>
+        <v>477034</v>
       </c>
       <c r="R9" t="n">
-        <v>6847394</v>
+        <v>6847389</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1538,7 +1538,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123771757</v>
+        <v>123771754</v>
       </c>
       <c r="B10" t="n">
         <v>98079</v>
@@ -1578,10 +1578,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>476911</v>
+        <v>476918</v>
       </c>
       <c r="R10" t="n">
-        <v>6847329</v>
+        <v>6847369</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1644,10 +1644,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123771718</v>
+        <v>123771746</v>
       </c>
       <c r="B11" t="n">
-        <v>79406</v>
+        <v>98079</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1656,25 +1656,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1684,10 +1684,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>477293</v>
+        <v>477174</v>
       </c>
       <c r="R11" t="n">
-        <v>6847591</v>
+        <v>6847450</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1750,7 +1750,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123771750</v>
+        <v>123771748</v>
       </c>
       <c r="B12" t="n">
         <v>98079</v>
@@ -1790,10 +1790,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>477093</v>
+        <v>477135</v>
       </c>
       <c r="R12" t="n">
-        <v>6847398</v>
+        <v>6847443</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1856,10 +1856,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123771759</v>
+        <v>123771763</v>
       </c>
       <c r="B13" t="n">
-        <v>78788</v>
+        <v>97996</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1868,25 +1868,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>219790</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1896,10 +1896,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>477096</v>
+        <v>476949</v>
       </c>
       <c r="R13" t="n">
-        <v>6847397</v>
+        <v>6847393</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1962,10 +1962,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123771748</v>
+        <v>123771733</v>
       </c>
       <c r="B14" t="n">
-        <v>98079</v>
+        <v>78525</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1974,25 +1974,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2002,10 +2002,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>477135</v>
+        <v>477300</v>
       </c>
       <c r="R14" t="n">
-        <v>6847443</v>
+        <v>6847594</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2068,10 +2068,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123771744</v>
+        <v>123771760</v>
       </c>
       <c r="B15" t="n">
-        <v>98079</v>
+        <v>78788</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2080,25 +2080,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2108,10 +2108,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>477281</v>
+        <v>477028</v>
       </c>
       <c r="R15" t="n">
-        <v>6847618</v>
+        <v>6847394</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2174,10 +2174,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123771746</v>
+        <v>123771718</v>
       </c>
       <c r="B16" t="n">
-        <v>98079</v>
+        <v>79406</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2186,25 +2186,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2214,10 +2214,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>477174</v>
+        <v>477293</v>
       </c>
       <c r="R16" t="n">
-        <v>6847450</v>
+        <v>6847591</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2280,10 +2280,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123771733</v>
+        <v>123771747</v>
       </c>
       <c r="B17" t="n">
-        <v>78525</v>
+        <v>98079</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2292,25 +2292,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2320,10 +2320,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>477300</v>
+        <v>477134</v>
       </c>
       <c r="R17" t="n">
-        <v>6847594</v>
+        <v>6847450</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2386,7 +2386,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123771749</v>
+        <v>123771756</v>
       </c>
       <c r="B18" t="n">
         <v>98079</v>
@@ -2426,10 +2426,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>477122</v>
+        <v>476937</v>
       </c>
       <c r="R18" t="n">
-        <v>6847410</v>
+        <v>6847291</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2462,6 +2462,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2024-07-26</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Minst 100 många i blom</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2492,7 +2497,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123771756</v>
+        <v>123771749</v>
       </c>
       <c r="B19" t="n">
         <v>98079</v>
@@ -2532,10 +2537,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>476937</v>
+        <v>477122</v>
       </c>
       <c r="R19" t="n">
-        <v>6847291</v>
+        <v>6847410</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2568,11 +2573,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2024-07-26</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Minst 100 många i blom</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2603,10 +2603,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123771732</v>
+        <v>123771744</v>
       </c>
       <c r="B20" t="n">
-        <v>79897</v>
+        <v>98079</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2615,25 +2615,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6461</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2643,10 +2643,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>477018</v>
+        <v>477281</v>
       </c>
       <c r="R20" t="n">
-        <v>6847382</v>
+        <v>6847618</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2709,7 +2709,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123771754</v>
+        <v>123771750</v>
       </c>
       <c r="B21" t="n">
         <v>98079</v>
@@ -2749,10 +2749,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>476918</v>
+        <v>477093</v>
       </c>
       <c r="R21" t="n">
-        <v>6847369</v>
+        <v>6847398</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2815,7 +2815,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123771752</v>
+        <v>123771745</v>
       </c>
       <c r="B22" t="n">
         <v>98079</v>
@@ -2855,10 +2855,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>477001</v>
+        <v>477255</v>
       </c>
       <c r="R22" t="n">
-        <v>6847417</v>
+        <v>6847445</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>

--- a/artfynd/A 31324-2024 artfynd.xlsx
+++ b/artfynd/A 31324-2024 artfynd.xlsx
@@ -897,7 +897,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123771753</v>
+        <v>123771752</v>
       </c>
       <c r="B4" t="n">
         <v>98079</v>
@@ -937,10 +937,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>476964</v>
+        <v>477001</v>
       </c>
       <c r="R4" t="n">
-        <v>6847387</v>
+        <v>6847417</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -973,11 +973,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-07-26</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Blomning över 80 stänglar</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1008,10 +1003,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123771752</v>
+        <v>123771763</v>
       </c>
       <c r="B5" t="n">
-        <v>98079</v>
+        <v>97996</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1020,25 +1015,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1048,10 +1043,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>477001</v>
+        <v>476949</v>
       </c>
       <c r="R5" t="n">
-        <v>6847417</v>
+        <v>6847393</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1114,10 +1109,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123771759</v>
+        <v>123771732</v>
       </c>
       <c r="B6" t="n">
-        <v>78788</v>
+        <v>79897</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1126,25 +1121,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>6461</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1154,10 +1149,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>477096</v>
+        <v>477018</v>
       </c>
       <c r="R6" t="n">
-        <v>6847397</v>
+        <v>6847382</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1220,7 +1215,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123771757</v>
+        <v>123771744</v>
       </c>
       <c r="B7" t="n">
         <v>98079</v>
@@ -1260,10 +1255,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>476911</v>
+        <v>477281</v>
       </c>
       <c r="R7" t="n">
-        <v>6847329</v>
+        <v>6847618</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1326,10 +1321,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123771732</v>
+        <v>123771718</v>
       </c>
       <c r="B8" t="n">
-        <v>79897</v>
+        <v>79406</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1338,25 +1333,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6461</v>
+        <v>6453</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1366,10 +1361,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>477018</v>
+        <v>477293</v>
       </c>
       <c r="R8" t="n">
-        <v>6847382</v>
+        <v>6847591</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1432,10 +1427,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123771751</v>
+        <v>123771760</v>
       </c>
       <c r="B9" t="n">
-        <v>98079</v>
+        <v>78788</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1444,25 +1439,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1472,10 +1467,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>477034</v>
+        <v>477028</v>
       </c>
       <c r="R9" t="n">
-        <v>6847389</v>
+        <v>6847394</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1644,7 +1639,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123771746</v>
+        <v>123771757</v>
       </c>
       <c r="B11" t="n">
         <v>98079</v>
@@ -1684,10 +1679,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>477174</v>
+        <v>476911</v>
       </c>
       <c r="R11" t="n">
-        <v>6847450</v>
+        <v>6847329</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1750,7 +1745,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123771748</v>
+        <v>123771753</v>
       </c>
       <c r="B12" t="n">
         <v>98079</v>
@@ -1790,10 +1785,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>477135</v>
+        <v>476964</v>
       </c>
       <c r="R12" t="n">
-        <v>6847443</v>
+        <v>6847387</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1826,6 +1821,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2024-07-26</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Blomning över 80 stänglar</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1856,10 +1856,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123771763</v>
+        <v>123771733</v>
       </c>
       <c r="B13" t="n">
-        <v>97996</v>
+        <v>78525</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1868,25 +1868,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>219790</v>
+        <v>228912</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1896,10 +1896,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>476949</v>
+        <v>477300</v>
       </c>
       <c r="R13" t="n">
-        <v>6847393</v>
+        <v>6847594</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1962,10 +1962,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123771733</v>
+        <v>123771756</v>
       </c>
       <c r="B14" t="n">
-        <v>78525</v>
+        <v>98079</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1974,25 +1974,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2002,10 +2002,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>477300</v>
+        <v>476937</v>
       </c>
       <c r="R14" t="n">
-        <v>6847594</v>
+        <v>6847291</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2038,6 +2038,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2024-07-26</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Minst 100 många i blom</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2068,10 +2073,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123771760</v>
+        <v>123771751</v>
       </c>
       <c r="B15" t="n">
-        <v>78788</v>
+        <v>98079</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2080,25 +2085,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2108,10 +2113,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>477028</v>
+        <v>477034</v>
       </c>
       <c r="R15" t="n">
-        <v>6847394</v>
+        <v>6847389</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2174,10 +2179,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123771718</v>
+        <v>123771747</v>
       </c>
       <c r="B16" t="n">
-        <v>79406</v>
+        <v>98079</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2186,25 +2191,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2214,10 +2219,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>477293</v>
+        <v>477134</v>
       </c>
       <c r="R16" t="n">
-        <v>6847591</v>
+        <v>6847450</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2280,7 +2285,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123771747</v>
+        <v>123771746</v>
       </c>
       <c r="B17" t="n">
         <v>98079</v>
@@ -2320,7 +2325,7 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>477134</v>
+        <v>477174</v>
       </c>
       <c r="R17" t="n">
         <v>6847450</v>
@@ -2386,7 +2391,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123771756</v>
+        <v>123771748</v>
       </c>
       <c r="B18" t="n">
         <v>98079</v>
@@ -2426,10 +2431,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>476937</v>
+        <v>477135</v>
       </c>
       <c r="R18" t="n">
-        <v>6847291</v>
+        <v>6847443</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2462,11 +2467,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2024-07-26</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Minst 100 många i blom</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2497,7 +2497,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123771749</v>
+        <v>123771745</v>
       </c>
       <c r="B19" t="n">
         <v>98079</v>
@@ -2537,10 +2537,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>477122</v>
+        <v>477255</v>
       </c>
       <c r="R19" t="n">
-        <v>6847410</v>
+        <v>6847445</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2603,10 +2603,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123771744</v>
+        <v>123771759</v>
       </c>
       <c r="B20" t="n">
-        <v>98079</v>
+        <v>78788</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2615,25 +2615,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2643,10 +2643,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>477281</v>
+        <v>477096</v>
       </c>
       <c r="R20" t="n">
-        <v>6847618</v>
+        <v>6847397</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2815,7 +2815,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123771745</v>
+        <v>123771749</v>
       </c>
       <c r="B22" t="n">
         <v>98079</v>
@@ -2855,10 +2855,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>477255</v>
+        <v>477122</v>
       </c>
       <c r="R22" t="n">
-        <v>6847445</v>
+        <v>6847410</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>

--- a/artfynd/A 31324-2024 artfynd.xlsx
+++ b/artfynd/A 31324-2024 artfynd.xlsx
@@ -1321,10 +1321,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123771718</v>
+        <v>123771760</v>
       </c>
       <c r="B8" t="n">
-        <v>79406</v>
+        <v>78788</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1337,21 +1337,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1361,10 +1361,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>477293</v>
+        <v>477028</v>
       </c>
       <c r="R8" t="n">
-        <v>6847591</v>
+        <v>6847394</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1427,10 +1427,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123771760</v>
+        <v>123771754</v>
       </c>
       <c r="B9" t="n">
-        <v>78788</v>
+        <v>98079</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1439,25 +1439,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1467,10 +1467,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>477028</v>
+        <v>476918</v>
       </c>
       <c r="R9" t="n">
-        <v>6847394</v>
+        <v>6847369</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1533,7 +1533,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123771754</v>
+        <v>123771757</v>
       </c>
       <c r="B10" t="n">
         <v>98079</v>
@@ -1573,10 +1573,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>476918</v>
+        <v>476911</v>
       </c>
       <c r="R10" t="n">
-        <v>6847369</v>
+        <v>6847329</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1639,7 +1639,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123771757</v>
+        <v>123771753</v>
       </c>
       <c r="B11" t="n">
         <v>98079</v>
@@ -1679,10 +1679,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>476911</v>
+        <v>476964</v>
       </c>
       <c r="R11" t="n">
-        <v>6847329</v>
+        <v>6847387</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1715,6 +1715,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2024-07-26</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Blomning över 80 stänglar</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1745,10 +1750,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123771753</v>
+        <v>123771733</v>
       </c>
       <c r="B12" t="n">
-        <v>98079</v>
+        <v>78525</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1757,25 +1762,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1785,10 +1790,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>476964</v>
+        <v>477300</v>
       </c>
       <c r="R12" t="n">
-        <v>6847387</v>
+        <v>6847594</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1821,11 +1826,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2024-07-26</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Blomning över 80 stänglar</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1856,10 +1856,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123771733</v>
+        <v>123771718</v>
       </c>
       <c r="B13" t="n">
-        <v>78525</v>
+        <v>79406</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1872,21 +1872,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1896,10 +1896,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>477300</v>
+        <v>477293</v>
       </c>
       <c r="R13" t="n">
-        <v>6847594</v>
+        <v>6847591</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -2179,7 +2179,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123771747</v>
+        <v>123771748</v>
       </c>
       <c r="B16" t="n">
         <v>98079</v>
@@ -2219,10 +2219,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>477134</v>
+        <v>477135</v>
       </c>
       <c r="R16" t="n">
-        <v>6847450</v>
+        <v>6847443</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2285,7 +2285,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123771746</v>
+        <v>123771747</v>
       </c>
       <c r="B17" t="n">
         <v>98079</v>
@@ -2325,7 +2325,7 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>477174</v>
+        <v>477134</v>
       </c>
       <c r="R17" t="n">
         <v>6847450</v>
@@ -2391,7 +2391,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123771748</v>
+        <v>123771746</v>
       </c>
       <c r="B18" t="n">
         <v>98079</v>
@@ -2431,10 +2431,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>477135</v>
+        <v>477174</v>
       </c>
       <c r="R18" t="n">
-        <v>6847443</v>
+        <v>6847450</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>

--- a/artfynd/A 31324-2024 artfynd.xlsx
+++ b/artfynd/A 31324-2024 artfynd.xlsx
@@ -897,7 +897,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123771752</v>
+        <v>123771744</v>
       </c>
       <c r="B4" t="n">
         <v>98079</v>
@@ -937,10 +937,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>477001</v>
+        <v>477281</v>
       </c>
       <c r="R4" t="n">
-        <v>6847417</v>
+        <v>6847618</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -1003,10 +1003,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123771763</v>
+        <v>123771756</v>
       </c>
       <c r="B5" t="n">
-        <v>97996</v>
+        <v>98079</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1015,25 +1015,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>219790</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1043,10 +1043,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>476949</v>
+        <v>476937</v>
       </c>
       <c r="R5" t="n">
-        <v>6847393</v>
+        <v>6847291</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1079,6 +1079,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-07-26</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Minst 100 många i blom</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1109,10 +1114,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123771732</v>
+        <v>123771763</v>
       </c>
       <c r="B6" t="n">
-        <v>79897</v>
+        <v>97996</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1125,21 +1130,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6461</v>
+        <v>219790</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1149,10 +1154,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>477018</v>
+        <v>476949</v>
       </c>
       <c r="R6" t="n">
-        <v>6847382</v>
+        <v>6847393</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1215,10 +1220,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123771744</v>
+        <v>123771718</v>
       </c>
       <c r="B7" t="n">
-        <v>98079</v>
+        <v>79406</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1227,25 +1232,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1255,10 +1260,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>477281</v>
+        <v>477293</v>
       </c>
       <c r="R7" t="n">
-        <v>6847618</v>
+        <v>6847591</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1321,7 +1326,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123771760</v>
+        <v>123771759</v>
       </c>
       <c r="B8" t="n">
         <v>78788</v>
@@ -1361,10 +1366,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>477028</v>
+        <v>477096</v>
       </c>
       <c r="R8" t="n">
-        <v>6847394</v>
+        <v>6847397</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1427,10 +1432,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123771754</v>
+        <v>123771760</v>
       </c>
       <c r="B9" t="n">
-        <v>98079</v>
+        <v>78788</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1439,25 +1444,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1467,10 +1472,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>476918</v>
+        <v>477028</v>
       </c>
       <c r="R9" t="n">
-        <v>6847369</v>
+        <v>6847394</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1533,7 +1538,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123771757</v>
+        <v>123771747</v>
       </c>
       <c r="B10" t="n">
         <v>98079</v>
@@ -1573,10 +1578,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>476911</v>
+        <v>477134</v>
       </c>
       <c r="R10" t="n">
-        <v>6847329</v>
+        <v>6847450</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1639,7 +1644,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123771753</v>
+        <v>123771754</v>
       </c>
       <c r="B11" t="n">
         <v>98079</v>
@@ -1679,10 +1684,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>476964</v>
+        <v>476918</v>
       </c>
       <c r="R11" t="n">
-        <v>6847387</v>
+        <v>6847369</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1715,11 +1720,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2024-07-26</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Blomning över 80 stänglar</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1750,10 +1750,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123771733</v>
+        <v>123771751</v>
       </c>
       <c r="B12" t="n">
-        <v>78525</v>
+        <v>98079</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1762,25 +1762,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1790,10 +1790,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>477300</v>
+        <v>477034</v>
       </c>
       <c r="R12" t="n">
-        <v>6847594</v>
+        <v>6847389</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1856,10 +1856,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123771718</v>
+        <v>123771745</v>
       </c>
       <c r="B13" t="n">
-        <v>79406</v>
+        <v>98079</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1868,25 +1868,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1896,10 +1896,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>477293</v>
+        <v>477255</v>
       </c>
       <c r="R13" t="n">
-        <v>6847591</v>
+        <v>6847445</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1962,7 +1962,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123771756</v>
+        <v>123771757</v>
       </c>
       <c r="B14" t="n">
         <v>98079</v>
@@ -2002,10 +2002,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>476937</v>
+        <v>476911</v>
       </c>
       <c r="R14" t="n">
-        <v>6847291</v>
+        <v>6847329</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2038,11 +2038,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2024-07-26</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Minst 100 många i blom</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2073,7 +2068,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123771751</v>
+        <v>123771753</v>
       </c>
       <c r="B15" t="n">
         <v>98079</v>
@@ -2113,10 +2108,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>477034</v>
+        <v>476964</v>
       </c>
       <c r="R15" t="n">
-        <v>6847389</v>
+        <v>6847387</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2149,6 +2144,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2024-07-26</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Blomning över 80 stänglar</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2179,7 +2179,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123771748</v>
+        <v>123771746</v>
       </c>
       <c r="B16" t="n">
         <v>98079</v>
@@ -2219,10 +2219,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>477135</v>
+        <v>477174</v>
       </c>
       <c r="R16" t="n">
-        <v>6847443</v>
+        <v>6847450</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2285,7 +2285,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123771747</v>
+        <v>123771749</v>
       </c>
       <c r="B17" t="n">
         <v>98079</v>
@@ -2325,10 +2325,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>477134</v>
+        <v>477122</v>
       </c>
       <c r="R17" t="n">
-        <v>6847450</v>
+        <v>6847410</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2391,10 +2391,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123771746</v>
+        <v>123771733</v>
       </c>
       <c r="B18" t="n">
-        <v>98079</v>
+        <v>78525</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2403,25 +2403,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2431,10 +2431,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>477174</v>
+        <v>477300</v>
       </c>
       <c r="R18" t="n">
-        <v>6847450</v>
+        <v>6847594</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2497,10 +2497,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123771745</v>
+        <v>123771732</v>
       </c>
       <c r="B19" t="n">
-        <v>98079</v>
+        <v>79897</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2509,25 +2509,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>6461</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2537,10 +2537,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>477255</v>
+        <v>477018</v>
       </c>
       <c r="R19" t="n">
-        <v>6847445</v>
+        <v>6847382</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2603,10 +2603,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123771759</v>
+        <v>123771752</v>
       </c>
       <c r="B20" t="n">
-        <v>78788</v>
+        <v>98079</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2615,25 +2615,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2643,10 +2643,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>477096</v>
+        <v>477001</v>
       </c>
       <c r="R20" t="n">
-        <v>6847397</v>
+        <v>6847417</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2709,7 +2709,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123771750</v>
+        <v>123771748</v>
       </c>
       <c r="B21" t="n">
         <v>98079</v>
@@ -2749,10 +2749,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>477093</v>
+        <v>477135</v>
       </c>
       <c r="R21" t="n">
-        <v>6847398</v>
+        <v>6847443</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2815,7 +2815,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123771749</v>
+        <v>123771750</v>
       </c>
       <c r="B22" t="n">
         <v>98079</v>
@@ -2855,10 +2855,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>477122</v>
+        <v>477093</v>
       </c>
       <c r="R22" t="n">
-        <v>6847410</v>
+        <v>6847398</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>

--- a/artfynd/A 31324-2024 artfynd.xlsx
+++ b/artfynd/A 31324-2024 artfynd.xlsx
@@ -897,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123771756</v>
+        <v>123771759</v>
       </c>
       <c r="B4" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -909,25 +909,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -937,10 +937,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>476937</v>
+        <v>477096</v>
       </c>
       <c r="R4" t="n">
-        <v>6847291</v>
+        <v>6847397</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -973,11 +973,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-07-26</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Minst 100 många i blom</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1008,7 +1003,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123771750</v>
+        <v>123771745</v>
       </c>
       <c r="B5" t="n">
         <v>98101</v>
@@ -1048,10 +1043,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>477093</v>
+        <v>477255</v>
       </c>
       <c r="R5" t="n">
-        <v>6847398</v>
+        <v>6847445</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1114,7 +1109,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123771744</v>
+        <v>123771747</v>
       </c>
       <c r="B6" t="n">
         <v>98101</v>
@@ -1154,10 +1149,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>477281</v>
+        <v>477134</v>
       </c>
       <c r="R6" t="n">
-        <v>6847618</v>
+        <v>6847450</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1220,10 +1215,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123771733</v>
+        <v>123771744</v>
       </c>
       <c r="B7" t="n">
-        <v>78547</v>
+        <v>98101</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1232,25 +1227,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1260,10 +1255,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>477300</v>
+        <v>477281</v>
       </c>
       <c r="R7" t="n">
-        <v>6847594</v>
+        <v>6847618</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1326,7 +1321,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123771749</v>
+        <v>123771746</v>
       </c>
       <c r="B8" t="n">
         <v>98101</v>
@@ -1366,10 +1361,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>477122</v>
+        <v>477174</v>
       </c>
       <c r="R8" t="n">
-        <v>6847410</v>
+        <v>6847450</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1432,10 +1427,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123771718</v>
+        <v>123771756</v>
       </c>
       <c r="B9" t="n">
-        <v>79428</v>
+        <v>98101</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1444,25 +1439,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1472,10 +1467,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>477293</v>
+        <v>476937</v>
       </c>
       <c r="R9" t="n">
-        <v>6847591</v>
+        <v>6847291</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1508,6 +1503,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2024-07-26</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Minst 100 många i blom</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1750,7 +1750,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123771757</v>
+        <v>123771750</v>
       </c>
       <c r="B12" t="n">
         <v>98101</v>
@@ -1790,10 +1790,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>476911</v>
+        <v>477093</v>
       </c>
       <c r="R12" t="n">
-        <v>6847329</v>
+        <v>6847398</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1856,7 +1856,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123771751</v>
+        <v>123771749</v>
       </c>
       <c r="B13" t="n">
         <v>98101</v>
@@ -1896,10 +1896,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>477034</v>
+        <v>477122</v>
       </c>
       <c r="R13" t="n">
-        <v>6847389</v>
+        <v>6847410</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1962,10 +1962,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123771732</v>
+        <v>123771718</v>
       </c>
       <c r="B14" t="n">
-        <v>79919</v>
+        <v>79428</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1974,25 +1974,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6461</v>
+        <v>6453</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2002,10 +2002,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>477018</v>
+        <v>477293</v>
       </c>
       <c r="R14" t="n">
-        <v>6847382</v>
+        <v>6847591</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2068,7 +2068,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123771747</v>
+        <v>123771754</v>
       </c>
       <c r="B15" t="n">
         <v>98101</v>
@@ -2108,10 +2108,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>477134</v>
+        <v>476918</v>
       </c>
       <c r="R15" t="n">
-        <v>6847450</v>
+        <v>6847369</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2174,7 +2174,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123771748</v>
+        <v>123771752</v>
       </c>
       <c r="B16" t="n">
         <v>98101</v>
@@ -2214,10 +2214,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>477135</v>
+        <v>477001</v>
       </c>
       <c r="R16" t="n">
-        <v>6847443</v>
+        <v>6847417</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2280,7 +2280,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123771753</v>
+        <v>123771748</v>
       </c>
       <c r="B17" t="n">
         <v>98101</v>
@@ -2320,10 +2320,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>476964</v>
+        <v>477135</v>
       </c>
       <c r="R17" t="n">
-        <v>6847387</v>
+        <v>6847443</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2356,11 +2356,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2024-07-26</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Blomning över 80 stänglar</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2391,7 +2386,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123771746</v>
+        <v>123771757</v>
       </c>
       <c r="B18" t="n">
         <v>98101</v>
@@ -2431,10 +2426,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>477174</v>
+        <v>476911</v>
       </c>
       <c r="R18" t="n">
-        <v>6847450</v>
+        <v>6847329</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2497,10 +2492,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123771745</v>
+        <v>123771733</v>
       </c>
       <c r="B19" t="n">
-        <v>98101</v>
+        <v>78547</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2509,25 +2504,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2537,10 +2532,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>477255</v>
+        <v>477300</v>
       </c>
       <c r="R19" t="n">
-        <v>6847445</v>
+        <v>6847594</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2603,10 +2598,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123771759</v>
+        <v>123771732</v>
       </c>
       <c r="B20" t="n">
-        <v>78810</v>
+        <v>79919</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2615,25 +2610,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>6461</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2643,10 +2638,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>477096</v>
+        <v>477018</v>
       </c>
       <c r="R20" t="n">
-        <v>6847397</v>
+        <v>6847382</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2709,7 +2704,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123771754</v>
+        <v>123771751</v>
       </c>
       <c r="B21" t="n">
         <v>98101</v>
@@ -2749,10 +2744,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>476918</v>
+        <v>477034</v>
       </c>
       <c r="R21" t="n">
-        <v>6847369</v>
+        <v>6847389</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2815,7 +2810,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123771752</v>
+        <v>123771753</v>
       </c>
       <c r="B22" t="n">
         <v>98101</v>
@@ -2855,10 +2850,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>477001</v>
+        <v>476964</v>
       </c>
       <c r="R22" t="n">
-        <v>6847417</v>
+        <v>6847387</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2891,6 +2886,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2024-07-26</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Blomning över 80 stänglar</t>
         </is>
       </c>
       <c r="AD22" t="b">

--- a/artfynd/A 31324-2024 artfynd.xlsx
+++ b/artfynd/A 31324-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY22"/>
+  <dimension ref="A1:AY43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2919,6 +2919,2116 @@
         </is>
       </c>
     </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>126059672</v>
+      </c>
+      <c r="B23" t="n">
+        <v>98334</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Kölsjöhållan, Kölsjöhållan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>477334</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6847619</v>
+      </c>
+      <c r="S23" t="n">
+        <v>15</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>126060190</v>
+      </c>
+      <c r="B24" t="n">
+        <v>98334</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Kölsjöhållan, Kölsjöhållan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>477091</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6847536</v>
+      </c>
+      <c r="S24" t="n">
+        <v>15</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>126060256</v>
+      </c>
+      <c r="B25" t="n">
+        <v>56843</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Kölsjöhållan, Kölsjöhållan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>477022</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6847543</v>
+      </c>
+      <c r="S25" t="n">
+        <v>15</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>126060370</v>
+      </c>
+      <c r="B26" t="n">
+        <v>98334</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Kölsjöhållan, Kölsjöhållan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>477008</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6847504</v>
+      </c>
+      <c r="S26" t="n">
+        <v>15</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>126059838</v>
+      </c>
+      <c r="B27" t="n">
+        <v>78727</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Kölsjöhållan, Kölsjöhållan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>477260</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6847508</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>126060401</v>
+      </c>
+      <c r="B28" t="n">
+        <v>98334</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Kölsjöhållan, Kölsjöhållan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>477001</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6847471</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>126057778</v>
+      </c>
+      <c r="B29" t="n">
+        <v>78968</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Kölsjöhållan, Kölsjöhållan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>476979</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6847356</v>
+      </c>
+      <c r="S29" t="n">
+        <v>15</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>126059586</v>
+      </c>
+      <c r="B30" t="n">
+        <v>98355</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Kölsjöhållan, Kölsjöhållan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>477373</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6847629</v>
+      </c>
+      <c r="S30" t="n">
+        <v>14</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>126059336</v>
+      </c>
+      <c r="B31" t="n">
+        <v>98355</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Kölsjöhållan, Kölsjöhållan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>477518</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6847579</v>
+      </c>
+      <c r="S31" t="n">
+        <v>15</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>126058004</v>
+      </c>
+      <c r="B32" t="n">
+        <v>78968</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Kölsjöhållan, Kölsjöhållan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>477074</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6847345</v>
+      </c>
+      <c r="S32" t="n">
+        <v>10</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>126059774</v>
+      </c>
+      <c r="B33" t="n">
+        <v>78968</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Kölsjöhållan, Kölsjöhållan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>477317</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6847536</v>
+      </c>
+      <c r="S33" t="n">
+        <v>12</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>126059386</v>
+      </c>
+      <c r="B34" t="n">
+        <v>80071</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Kölsjöhållan, Kölsjöhållan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>477486</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6847598</v>
+      </c>
+      <c r="S34" t="n">
+        <v>15</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>126059644</v>
+      </c>
+      <c r="B35" t="n">
+        <v>78968</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Kölsjöhållan, Kölsjöhållan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>477338</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6847624</v>
+      </c>
+      <c r="S35" t="n">
+        <v>15</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>126057983</v>
+      </c>
+      <c r="B36" t="n">
+        <v>78968</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Kölsjöhållan, Kölsjöhållan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>477073</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6847347</v>
+      </c>
+      <c r="S36" t="n">
+        <v>15</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>126057797</v>
+      </c>
+      <c r="B37" t="n">
+        <v>98334</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Kölsjöhållan, Kölsjöhållan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>476979</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6847360</v>
+      </c>
+      <c r="S37" t="n">
+        <v>15</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>126057698</v>
+      </c>
+      <c r="B38" t="n">
+        <v>80071</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Kölsjöhållan, Kölsjöhållan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>476959</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6847356</v>
+      </c>
+      <c r="S38" t="n">
+        <v>15</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>126059357</v>
+      </c>
+      <c r="B39" t="n">
+        <v>98334</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Kölsjöhållan, Kölsjöhållan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>477503</v>
+      </c>
+      <c r="R39" t="n">
+        <v>6847581</v>
+      </c>
+      <c r="S39" t="n">
+        <v>15</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>126059744</v>
+      </c>
+      <c r="B40" t="n">
+        <v>98334</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Kölsjöhållan, Kölsjöhållan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>477337</v>
+      </c>
+      <c r="R40" t="n">
+        <v>6847567</v>
+      </c>
+      <c r="S40" t="n">
+        <v>15</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>126058294</v>
+      </c>
+      <c r="B41" t="n">
+        <v>78968</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Kölsjöhållan, Kölsjöhållan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>477208</v>
+      </c>
+      <c r="R41" t="n">
+        <v>6847469</v>
+      </c>
+      <c r="S41" t="n">
+        <v>15</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>126059509</v>
+      </c>
+      <c r="B42" t="n">
+        <v>98334</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Kölsjöhållan, Kölsjöhållan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>477425</v>
+      </c>
+      <c r="R42" t="n">
+        <v>6847606</v>
+      </c>
+      <c r="S42" t="n">
+        <v>15</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>126060437</v>
+      </c>
+      <c r="B43" t="n">
+        <v>98334</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>130</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Kölsjöhållan, Kölsjöhållan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>476993</v>
+      </c>
+      <c r="R43" t="n">
+        <v>6847457</v>
+      </c>
+      <c r="S43" t="n">
+        <v>15</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 31324-2024 artfynd.xlsx
+++ b/artfynd/A 31324-2024 artfynd.xlsx
@@ -2921,10 +2921,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>126059672</v>
+        <v>126060190</v>
       </c>
       <c r="B23" t="n">
-        <v>98334</v>
+        <v>98338</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2951,7 +2951,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>90</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -2965,10 +2965,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>477334</v>
+        <v>477091</v>
       </c>
       <c r="R23" t="n">
-        <v>6847619</v>
+        <v>6847536</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -3027,10 +3027,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>126060190</v>
+        <v>126059672</v>
       </c>
       <c r="B24" t="n">
-        <v>98334</v>
+        <v>98338</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3057,7 +3057,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>80</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -3071,10 +3071,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>477091</v>
+        <v>477334</v>
       </c>
       <c r="R24" t="n">
-        <v>6847536</v>
+        <v>6847619</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -3243,7 +3243,7 @@
         <v>126060370</v>
       </c>
       <c r="B26" t="n">
-        <v>98334</v>
+        <v>98338</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3337,45 +3337,54 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>126059838</v>
+        <v>126060401</v>
       </c>
       <c r="B27" t="n">
-        <v>78727</v>
+        <v>98338</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Kölsjöhållan, Kölsjöhållan, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>477260</v>
+        <v>477001</v>
       </c>
       <c r="R27" t="n">
-        <v>6847508</v>
+        <v>6847471</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3434,54 +3443,45 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>126060401</v>
+        <v>126059838</v>
       </c>
       <c r="B28" t="n">
-        <v>98334</v>
+        <v>78731</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Kölsjöhållan, Kölsjöhållan, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>477001</v>
+        <v>477260</v>
       </c>
       <c r="R28" t="n">
-        <v>6847471</v>
+        <v>6847508</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3540,32 +3540,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126057778</v>
+        <v>126059586</v>
       </c>
       <c r="B29" t="n">
-        <v>78968</v>
+        <v>98359</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3575,13 +3575,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>476979</v>
+        <v>477373</v>
       </c>
       <c r="R29" t="n">
-        <v>6847356</v>
+        <v>6847629</v>
       </c>
       <c r="S29" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3637,32 +3637,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>126059586</v>
+        <v>126057778</v>
       </c>
       <c r="B30" t="n">
-        <v>98355</v>
+        <v>78972</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3672,13 +3672,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>477373</v>
+        <v>476979</v>
       </c>
       <c r="R30" t="n">
-        <v>6847629</v>
+        <v>6847356</v>
       </c>
       <c r="S30" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3734,32 +3734,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>126059336</v>
+        <v>126058004</v>
       </c>
       <c r="B31" t="n">
-        <v>98355</v>
+        <v>78972</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3769,13 +3769,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>477518</v>
+        <v>477074</v>
       </c>
       <c r="R31" t="n">
-        <v>6847579</v>
+        <v>6847345</v>
       </c>
       <c r="S31" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3831,32 +3831,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>126058004</v>
+        <v>126059336</v>
       </c>
       <c r="B32" t="n">
-        <v>78968</v>
+        <v>98359</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3866,13 +3866,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>477074</v>
+        <v>477518</v>
       </c>
       <c r="R32" t="n">
-        <v>6847345</v>
+        <v>6847579</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3931,7 +3931,7 @@
         <v>126059774</v>
       </c>
       <c r="B33" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4028,7 +4028,7 @@
         <v>126059386</v>
       </c>
       <c r="B34" t="n">
-        <v>80071</v>
+        <v>80075</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4125,7 +4125,7 @@
         <v>126059644</v>
       </c>
       <c r="B35" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4222,7 +4222,7 @@
         <v>126057983</v>
       </c>
       <c r="B36" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4319,7 +4319,7 @@
         <v>126057797</v>
       </c>
       <c r="B37" t="n">
-        <v>98334</v>
+        <v>98338</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4425,7 +4425,7 @@
         <v>126057698</v>
       </c>
       <c r="B38" t="n">
-        <v>80071</v>
+        <v>80075</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4519,10 +4519,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>126059357</v>
+        <v>126059744</v>
       </c>
       <c r="B39" t="n">
-        <v>98334</v>
+        <v>98338</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4547,26 +4547,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Kölsjöhållan, Kölsjöhållan, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>477503</v>
+        <v>477337</v>
       </c>
       <c r="R39" t="n">
-        <v>6847581</v>
+        <v>6847567</v>
       </c>
       <c r="S39" t="n">
         <v>15</v>
@@ -4625,10 +4616,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>126059744</v>
+        <v>126059357</v>
       </c>
       <c r="B40" t="n">
-        <v>98334</v>
+        <v>98338</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4653,17 +4644,26 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I40" t="inlineStr"/>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Kölsjöhållan, Kölsjöhållan, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>477337</v>
+        <v>477503</v>
       </c>
       <c r="R40" t="n">
-        <v>6847567</v>
+        <v>6847581</v>
       </c>
       <c r="S40" t="n">
         <v>15</v>
@@ -4722,45 +4722,54 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>126058294</v>
+        <v>126059509</v>
       </c>
       <c r="B41" t="n">
-        <v>78968</v>
+        <v>98338</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Kölsjöhållan, Kölsjöhållan, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>477208</v>
+        <v>477425</v>
       </c>
       <c r="R41" t="n">
-        <v>6847469</v>
+        <v>6847606</v>
       </c>
       <c r="S41" t="n">
         <v>15</v>
@@ -4819,10 +4828,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>126059509</v>
+        <v>126060437</v>
       </c>
       <c r="B42" t="n">
-        <v>98334</v>
+        <v>98338</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4849,7 +4858,7 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>130</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -4863,10 +4872,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>477425</v>
+        <v>476993</v>
       </c>
       <c r="R42" t="n">
-        <v>6847606</v>
+        <v>6847457</v>
       </c>
       <c r="S42" t="n">
         <v>15</v>
@@ -4925,54 +4934,45 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>126060437</v>
+        <v>126058294</v>
       </c>
       <c r="B43" t="n">
-        <v>98334</v>
+        <v>78972</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>130</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Kölsjöhållan, Kölsjöhållan, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>476993</v>
+        <v>477208</v>
       </c>
       <c r="R43" t="n">
-        <v>6847457</v>
+        <v>6847469</v>
       </c>
       <c r="S43" t="n">
         <v>15</v>

--- a/artfynd/A 31324-2024 artfynd.xlsx
+++ b/artfynd/A 31324-2024 artfynd.xlsx
@@ -2924,7 +2924,7 @@
         <v>126060190</v>
       </c>
       <c r="B23" t="n">
-        <v>98338</v>
+        <v>98339</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3030,7 +3030,7 @@
         <v>126059672</v>
       </c>
       <c r="B24" t="n">
-        <v>98338</v>
+        <v>98339</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3243,7 +3243,7 @@
         <v>126060370</v>
       </c>
       <c r="B26" t="n">
-        <v>98338</v>
+        <v>98339</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3340,7 +3340,7 @@
         <v>126060401</v>
       </c>
       <c r="B27" t="n">
-        <v>98338</v>
+        <v>98339</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3540,32 +3540,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126059586</v>
+        <v>126057778</v>
       </c>
       <c r="B29" t="n">
-        <v>98359</v>
+        <v>78972</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3575,13 +3575,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>477373</v>
+        <v>476979</v>
       </c>
       <c r="R29" t="n">
-        <v>6847629</v>
+        <v>6847356</v>
       </c>
       <c r="S29" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3637,32 +3637,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>126057778</v>
+        <v>126059586</v>
       </c>
       <c r="B30" t="n">
-        <v>78972</v>
+        <v>98360</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3672,13 +3672,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>476979</v>
+        <v>477373</v>
       </c>
       <c r="R30" t="n">
-        <v>6847356</v>
+        <v>6847629</v>
       </c>
       <c r="S30" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3734,32 +3734,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>126058004</v>
+        <v>126059336</v>
       </c>
       <c r="B31" t="n">
-        <v>78972</v>
+        <v>98360</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3769,13 +3769,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>477074</v>
+        <v>477518</v>
       </c>
       <c r="R31" t="n">
-        <v>6847345</v>
+        <v>6847579</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3831,32 +3831,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>126059336</v>
+        <v>126058004</v>
       </c>
       <c r="B32" t="n">
-        <v>98359</v>
+        <v>78972</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3866,13 +3866,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>477518</v>
+        <v>477074</v>
       </c>
       <c r="R32" t="n">
-        <v>6847579</v>
+        <v>6847345</v>
       </c>
       <c r="S32" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4025,10 +4025,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>126059386</v>
+        <v>126059644</v>
       </c>
       <c r="B34" t="n">
-        <v>80075</v>
+        <v>78972</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4036,21 +4036,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4060,10 +4060,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>477486</v>
+        <v>477338</v>
       </c>
       <c r="R34" t="n">
-        <v>6847598</v>
+        <v>6847624</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -4122,7 +4122,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>126059644</v>
+        <v>126057983</v>
       </c>
       <c r="B35" t="n">
         <v>78972</v>
@@ -4157,10 +4157,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>477338</v>
+        <v>477073</v>
       </c>
       <c r="R35" t="n">
-        <v>6847624</v>
+        <v>6847347</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>
@@ -4219,10 +4219,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>126057983</v>
+        <v>126059386</v>
       </c>
       <c r="B36" t="n">
-        <v>78972</v>
+        <v>80075</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4230,21 +4230,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4254,10 +4254,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>477073</v>
+        <v>477486</v>
       </c>
       <c r="R36" t="n">
-        <v>6847347</v>
+        <v>6847598</v>
       </c>
       <c r="S36" t="n">
         <v>15</v>
@@ -4319,7 +4319,7 @@
         <v>126057797</v>
       </c>
       <c r="B37" t="n">
-        <v>98338</v>
+        <v>98339</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4522,7 +4522,7 @@
         <v>126059744</v>
       </c>
       <c r="B39" t="n">
-        <v>98338</v>
+        <v>98339</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4619,7 +4619,7 @@
         <v>126059357</v>
       </c>
       <c r="B40" t="n">
-        <v>98338</v>
+        <v>98339</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4722,54 +4722,45 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>126059509</v>
+        <v>126058294</v>
       </c>
       <c r="B41" t="n">
-        <v>98338</v>
+        <v>78972</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Kölsjöhållan, Kölsjöhållan, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>477425</v>
+        <v>477208</v>
       </c>
       <c r="R41" t="n">
-        <v>6847606</v>
+        <v>6847469</v>
       </c>
       <c r="S41" t="n">
         <v>15</v>
@@ -4828,10 +4819,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>126060437</v>
+        <v>126059509</v>
       </c>
       <c r="B42" t="n">
-        <v>98338</v>
+        <v>98339</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4858,7 +4849,7 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>130</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -4872,10 +4863,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>476993</v>
+        <v>477425</v>
       </c>
       <c r="R42" t="n">
-        <v>6847457</v>
+        <v>6847606</v>
       </c>
       <c r="S42" t="n">
         <v>15</v>
@@ -4934,45 +4925,54 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>126058294</v>
+        <v>126060437</v>
       </c>
       <c r="B43" t="n">
-        <v>78972</v>
+        <v>98339</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>130</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Kölsjöhållan, Kölsjöhållan, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>477208</v>
+        <v>476993</v>
       </c>
       <c r="R43" t="n">
-        <v>6847469</v>
+        <v>6847457</v>
       </c>
       <c r="S43" t="n">
         <v>15</v>

--- a/artfynd/A 31324-2024 artfynd.xlsx
+++ b/artfynd/A 31324-2024 artfynd.xlsx
@@ -3734,32 +3734,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>126059336</v>
+        <v>126058004</v>
       </c>
       <c r="B31" t="n">
-        <v>98360</v>
+        <v>78972</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3769,13 +3769,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>477518</v>
+        <v>477074</v>
       </c>
       <c r="R31" t="n">
-        <v>6847579</v>
+        <v>6847345</v>
       </c>
       <c r="S31" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3831,32 +3831,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>126058004</v>
+        <v>126059336</v>
       </c>
       <c r="B32" t="n">
-        <v>78972</v>
+        <v>98360</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3866,13 +3866,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>477074</v>
+        <v>477518</v>
       </c>
       <c r="R32" t="n">
-        <v>6847345</v>
+        <v>6847579</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>

--- a/artfynd/A 31324-2024 artfynd.xlsx
+++ b/artfynd/A 31324-2024 artfynd.xlsx
@@ -4316,54 +4316,45 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>126057797</v>
+        <v>126057698</v>
       </c>
       <c r="B37" t="n">
-        <v>98339</v>
+        <v>80075</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Kölsjöhållan, Kölsjöhållan, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>476979</v>
+        <v>476959</v>
       </c>
       <c r="R37" t="n">
-        <v>6847360</v>
+        <v>6847356</v>
       </c>
       <c r="S37" t="n">
         <v>15</v>
@@ -4422,45 +4413,54 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>126057698</v>
+        <v>126057797</v>
       </c>
       <c r="B38" t="n">
-        <v>80075</v>
+        <v>98339</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Kölsjöhållan, Kölsjöhållan, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>476959</v>
+        <v>476979</v>
       </c>
       <c r="R38" t="n">
-        <v>6847356</v>
+        <v>6847360</v>
       </c>
       <c r="S38" t="n">
         <v>15</v>

--- a/artfynd/A 31324-2024 artfynd.xlsx
+++ b/artfynd/A 31324-2024 artfynd.xlsx
@@ -2921,10 +2921,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>126060190</v>
+        <v>126059672</v>
       </c>
       <c r="B23" t="n">
-        <v>98339</v>
+        <v>98341</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2951,7 +2951,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>80</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -2965,10 +2965,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>477091</v>
+        <v>477334</v>
       </c>
       <c r="R23" t="n">
-        <v>6847536</v>
+        <v>6847619</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -3027,10 +3027,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>126059672</v>
+        <v>126060190</v>
       </c>
       <c r="B24" t="n">
-        <v>98339</v>
+        <v>98341</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3057,7 +3057,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>90</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -3071,10 +3071,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>477334</v>
+        <v>477091</v>
       </c>
       <c r="R24" t="n">
-        <v>6847619</v>
+        <v>6847536</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -3136,7 +3136,7 @@
         <v>126060256</v>
       </c>
       <c r="B25" t="n">
-        <v>56843</v>
+        <v>56844</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3243,7 +3243,7 @@
         <v>126060370</v>
       </c>
       <c r="B26" t="n">
-        <v>98339</v>
+        <v>98341</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3337,54 +3337,45 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>126060401</v>
+        <v>126059838</v>
       </c>
       <c r="B27" t="n">
-        <v>98339</v>
+        <v>78732</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Kölsjöhållan, Kölsjöhållan, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>477001</v>
+        <v>477260</v>
       </c>
       <c r="R27" t="n">
-        <v>6847471</v>
+        <v>6847508</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3443,45 +3434,54 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>126059838</v>
+        <v>126060401</v>
       </c>
       <c r="B28" t="n">
-        <v>78731</v>
+        <v>98341</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Kölsjöhållan, Kölsjöhållan, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>477260</v>
+        <v>477001</v>
       </c>
       <c r="R28" t="n">
-        <v>6847508</v>
+        <v>6847471</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3543,7 +3543,7 @@
         <v>126057778</v>
       </c>
       <c r="B29" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3640,7 +3640,7 @@
         <v>126059586</v>
       </c>
       <c r="B30" t="n">
-        <v>98360</v>
+        <v>98362</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3737,7 +3737,7 @@
         <v>126058004</v>
       </c>
       <c r="B31" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3834,7 +3834,7 @@
         <v>126059336</v>
       </c>
       <c r="B32" t="n">
-        <v>98360</v>
+        <v>98362</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3931,7 +3931,7 @@
         <v>126059774</v>
       </c>
       <c r="B33" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4028,7 +4028,7 @@
         <v>126059644</v>
       </c>
       <c r="B34" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4125,7 +4125,7 @@
         <v>126057983</v>
       </c>
       <c r="B35" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4222,7 +4222,7 @@
         <v>126059386</v>
       </c>
       <c r="B36" t="n">
-        <v>80075</v>
+        <v>80076</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4316,45 +4316,54 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>126057698</v>
+        <v>126057797</v>
       </c>
       <c r="B37" t="n">
-        <v>80075</v>
+        <v>98341</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Kölsjöhållan, Kölsjöhållan, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>476959</v>
+        <v>476979</v>
       </c>
       <c r="R37" t="n">
-        <v>6847356</v>
+        <v>6847360</v>
       </c>
       <c r="S37" t="n">
         <v>15</v>
@@ -4413,54 +4422,45 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>126057797</v>
+        <v>126057698</v>
       </c>
       <c r="B38" t="n">
-        <v>98339</v>
+        <v>80076</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Kölsjöhållan, Kölsjöhållan, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>476979</v>
+        <v>476959</v>
       </c>
       <c r="R38" t="n">
-        <v>6847360</v>
+        <v>6847356</v>
       </c>
       <c r="S38" t="n">
         <v>15</v>
@@ -4519,10 +4519,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>126059744</v>
+        <v>126059357</v>
       </c>
       <c r="B39" t="n">
-        <v>98339</v>
+        <v>98341</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4547,17 +4547,26 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I39" t="inlineStr"/>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Kölsjöhållan, Kölsjöhållan, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>477337</v>
+        <v>477503</v>
       </c>
       <c r="R39" t="n">
-        <v>6847567</v>
+        <v>6847581</v>
       </c>
       <c r="S39" t="n">
         <v>15</v>
@@ -4616,10 +4625,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>126059357</v>
+        <v>126059744</v>
       </c>
       <c r="B40" t="n">
-        <v>98339</v>
+        <v>98341</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4644,26 +4653,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Kölsjöhållan, Kölsjöhållan, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>477503</v>
+        <v>477337</v>
       </c>
       <c r="R40" t="n">
-        <v>6847581</v>
+        <v>6847567</v>
       </c>
       <c r="S40" t="n">
         <v>15</v>
@@ -4725,7 +4725,7 @@
         <v>126058294</v>
       </c>
       <c r="B41" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4819,10 +4819,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>126059509</v>
+        <v>126060437</v>
       </c>
       <c r="B42" t="n">
-        <v>98339</v>
+        <v>98341</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4849,7 +4849,7 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>130</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -4863,10 +4863,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>477425</v>
+        <v>476993</v>
       </c>
       <c r="R42" t="n">
-        <v>6847606</v>
+        <v>6847457</v>
       </c>
       <c r="S42" t="n">
         <v>15</v>
@@ -4925,10 +4925,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>126060437</v>
+        <v>126059509</v>
       </c>
       <c r="B43" t="n">
-        <v>98339</v>
+        <v>98341</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4955,7 +4955,7 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>130</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -4969,10 +4969,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>476993</v>
+        <v>477425</v>
       </c>
       <c r="R43" t="n">
-        <v>6847457</v>
+        <v>6847606</v>
       </c>
       <c r="S43" t="n">
         <v>15</v>

--- a/artfynd/A 31324-2024 artfynd.xlsx
+++ b/artfynd/A 31324-2024 artfynd.xlsx
@@ -3734,32 +3734,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>126058004</v>
+        <v>126059336</v>
       </c>
       <c r="B31" t="n">
-        <v>78973</v>
+        <v>98362</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3769,13 +3769,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>477074</v>
+        <v>477518</v>
       </c>
       <c r="R31" t="n">
-        <v>6847345</v>
+        <v>6847579</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3831,32 +3831,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>126059336</v>
+        <v>126058004</v>
       </c>
       <c r="B32" t="n">
-        <v>98362</v>
+        <v>78973</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3866,13 +3866,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>477518</v>
+        <v>477074</v>
       </c>
       <c r="R32" t="n">
-        <v>6847579</v>
+        <v>6847345</v>
       </c>
       <c r="S32" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>

--- a/artfynd/A 31324-2024 artfynd.xlsx
+++ b/artfynd/A 31324-2024 artfynd.xlsx
@@ -2921,10 +2921,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>126059672</v>
+        <v>126060190</v>
       </c>
       <c r="B23" t="n">
-        <v>98341</v>
+        <v>98343</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2951,7 +2951,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>90</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -2965,10 +2965,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>477334</v>
+        <v>477091</v>
       </c>
       <c r="R23" t="n">
-        <v>6847619</v>
+        <v>6847536</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -3027,10 +3027,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>126060190</v>
+        <v>126059672</v>
       </c>
       <c r="B24" t="n">
-        <v>98341</v>
+        <v>98343</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3057,7 +3057,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>80</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -3071,10 +3071,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>477091</v>
+        <v>477334</v>
       </c>
       <c r="R24" t="n">
-        <v>6847536</v>
+        <v>6847619</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -3243,7 +3243,7 @@
         <v>126060370</v>
       </c>
       <c r="B26" t="n">
-        <v>98341</v>
+        <v>98343</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3337,45 +3337,54 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>126059838</v>
+        <v>126060401</v>
       </c>
       <c r="B27" t="n">
-        <v>78732</v>
+        <v>98343</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Kölsjöhållan, Kölsjöhållan, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>477260</v>
+        <v>477001</v>
       </c>
       <c r="R27" t="n">
-        <v>6847508</v>
+        <v>6847471</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3434,54 +3443,45 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>126060401</v>
+        <v>126059838</v>
       </c>
       <c r="B28" t="n">
-        <v>98341</v>
+        <v>78732</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Kölsjöhållan, Kölsjöhållan, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>477001</v>
+        <v>477260</v>
       </c>
       <c r="R28" t="n">
-        <v>6847471</v>
+        <v>6847508</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3640,7 +3640,7 @@
         <v>126059586</v>
       </c>
       <c r="B30" t="n">
-        <v>98362</v>
+        <v>98364</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3734,32 +3734,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>126059336</v>
+        <v>126058004</v>
       </c>
       <c r="B31" t="n">
-        <v>98362</v>
+        <v>78973</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3769,13 +3769,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>477518</v>
+        <v>477074</v>
       </c>
       <c r="R31" t="n">
-        <v>6847579</v>
+        <v>6847345</v>
       </c>
       <c r="S31" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3831,32 +3831,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>126058004</v>
+        <v>126059336</v>
       </c>
       <c r="B32" t="n">
-        <v>78973</v>
+        <v>98364</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3866,13 +3866,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>477074</v>
+        <v>477518</v>
       </c>
       <c r="R32" t="n">
-        <v>6847345</v>
+        <v>6847579</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4316,54 +4316,45 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>126057797</v>
+        <v>126057698</v>
       </c>
       <c r="B37" t="n">
-        <v>98341</v>
+        <v>80076</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Kölsjöhållan, Kölsjöhållan, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>476979</v>
+        <v>476959</v>
       </c>
       <c r="R37" t="n">
-        <v>6847360</v>
+        <v>6847356</v>
       </c>
       <c r="S37" t="n">
         <v>15</v>
@@ -4422,45 +4413,54 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>126057698</v>
+        <v>126057797</v>
       </c>
       <c r="B38" t="n">
-        <v>80076</v>
+        <v>98343</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Kölsjöhållan, Kölsjöhållan, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>476959</v>
+        <v>476979</v>
       </c>
       <c r="R38" t="n">
-        <v>6847356</v>
+        <v>6847360</v>
       </c>
       <c r="S38" t="n">
         <v>15</v>
@@ -4519,10 +4519,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>126059357</v>
+        <v>126059744</v>
       </c>
       <c r="B39" t="n">
-        <v>98341</v>
+        <v>98343</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4547,26 +4547,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Kölsjöhållan, Kölsjöhållan, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>477503</v>
+        <v>477337</v>
       </c>
       <c r="R39" t="n">
-        <v>6847581</v>
+        <v>6847567</v>
       </c>
       <c r="S39" t="n">
         <v>15</v>
@@ -4625,10 +4616,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>126059744</v>
+        <v>126059357</v>
       </c>
       <c r="B40" t="n">
-        <v>98341</v>
+        <v>98343</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4653,17 +4644,26 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I40" t="inlineStr"/>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Kölsjöhållan, Kölsjöhållan, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>477337</v>
+        <v>477503</v>
       </c>
       <c r="R40" t="n">
-        <v>6847567</v>
+        <v>6847581</v>
       </c>
       <c r="S40" t="n">
         <v>15</v>
@@ -4819,10 +4819,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>126060437</v>
+        <v>126059509</v>
       </c>
       <c r="B42" t="n">
-        <v>98341</v>
+        <v>98343</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4849,7 +4849,7 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>130</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -4863,10 +4863,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>476993</v>
+        <v>477425</v>
       </c>
       <c r="R42" t="n">
-        <v>6847457</v>
+        <v>6847606</v>
       </c>
       <c r="S42" t="n">
         <v>15</v>
@@ -4925,10 +4925,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>126059509</v>
+        <v>126060437</v>
       </c>
       <c r="B43" t="n">
-        <v>98341</v>
+        <v>98343</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4955,7 +4955,7 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>130</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -4969,10 +4969,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>477425</v>
+        <v>476993</v>
       </c>
       <c r="R43" t="n">
-        <v>6847606</v>
+        <v>6847457</v>
       </c>
       <c r="S43" t="n">
         <v>15</v>

--- a/artfynd/A 31324-2024 artfynd.xlsx
+++ b/artfynd/A 31324-2024 artfynd.xlsx
@@ -4025,10 +4025,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>126059644</v>
+        <v>126059386</v>
       </c>
       <c r="B34" t="n">
-        <v>78973</v>
+        <v>80076</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4036,21 +4036,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4060,10 +4060,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>477338</v>
+        <v>477486</v>
       </c>
       <c r="R34" t="n">
-        <v>6847624</v>
+        <v>6847598</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -4122,7 +4122,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>126057983</v>
+        <v>126059644</v>
       </c>
       <c r="B35" t="n">
         <v>78973</v>
@@ -4157,10 +4157,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>477073</v>
+        <v>477338</v>
       </c>
       <c r="R35" t="n">
-        <v>6847347</v>
+        <v>6847624</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>
@@ -4219,10 +4219,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>126059386</v>
+        <v>126057983</v>
       </c>
       <c r="B36" t="n">
-        <v>80076</v>
+        <v>78973</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4230,21 +4230,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4254,10 +4254,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>477486</v>
+        <v>477073</v>
       </c>
       <c r="R36" t="n">
-        <v>6847598</v>
+        <v>6847347</v>
       </c>
       <c r="S36" t="n">
         <v>15</v>

--- a/artfynd/A 31324-2024 artfynd.xlsx
+++ b/artfynd/A 31324-2024 artfynd.xlsx
@@ -2924,7 +2924,7 @@
         <v>126060190</v>
       </c>
       <c r="B23" t="n">
-        <v>98343</v>
+        <v>98345</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3030,7 +3030,7 @@
         <v>126059672</v>
       </c>
       <c r="B24" t="n">
-        <v>98343</v>
+        <v>98345</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3243,7 +3243,7 @@
         <v>126060370</v>
       </c>
       <c r="B26" t="n">
-        <v>98343</v>
+        <v>98345</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3340,7 +3340,7 @@
         <v>126060401</v>
       </c>
       <c r="B27" t="n">
-        <v>98343</v>
+        <v>98345</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3640,7 +3640,7 @@
         <v>126059586</v>
       </c>
       <c r="B30" t="n">
-        <v>98364</v>
+        <v>98366</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3834,7 +3834,7 @@
         <v>126059336</v>
       </c>
       <c r="B32" t="n">
-        <v>98364</v>
+        <v>98366</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4416,7 +4416,7 @@
         <v>126057797</v>
       </c>
       <c r="B38" t="n">
-        <v>98343</v>
+        <v>98345</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4522,7 +4522,7 @@
         <v>126059744</v>
       </c>
       <c r="B39" t="n">
-        <v>98343</v>
+        <v>98345</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4619,7 +4619,7 @@
         <v>126059357</v>
       </c>
       <c r="B40" t="n">
-        <v>98343</v>
+        <v>98345</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4722,45 +4722,54 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>126058294</v>
+        <v>126059509</v>
       </c>
       <c r="B41" t="n">
-        <v>78973</v>
+        <v>98345</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Kölsjöhållan, Kölsjöhållan, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>477208</v>
+        <v>477425</v>
       </c>
       <c r="R41" t="n">
-        <v>6847469</v>
+        <v>6847606</v>
       </c>
       <c r="S41" t="n">
         <v>15</v>
@@ -4819,10 +4828,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>126059509</v>
+        <v>126060437</v>
       </c>
       <c r="B42" t="n">
-        <v>98343</v>
+        <v>98345</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4849,7 +4858,7 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>130</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -4863,10 +4872,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>477425</v>
+        <v>476993</v>
       </c>
       <c r="R42" t="n">
-        <v>6847606</v>
+        <v>6847457</v>
       </c>
       <c r="S42" t="n">
         <v>15</v>
@@ -4925,54 +4934,45 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>126060437</v>
+        <v>126058294</v>
       </c>
       <c r="B43" t="n">
-        <v>98343</v>
+        <v>78973</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>130</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Kölsjöhållan, Kölsjöhållan, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>476993</v>
+        <v>477208</v>
       </c>
       <c r="R43" t="n">
-        <v>6847457</v>
+        <v>6847469</v>
       </c>
       <c r="S43" t="n">
         <v>15</v>

--- a/artfynd/A 31324-2024 artfynd.xlsx
+++ b/artfynd/A 31324-2024 artfynd.xlsx
@@ -2924,7 +2924,7 @@
         <v>126060190</v>
       </c>
       <c r="B23" t="n">
-        <v>98345</v>
+        <v>98349</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3030,7 +3030,7 @@
         <v>126059672</v>
       </c>
       <c r="B24" t="n">
-        <v>98345</v>
+        <v>98349</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3136,7 +3136,7 @@
         <v>126060256</v>
       </c>
       <c r="B25" t="n">
-        <v>56844</v>
+        <v>56848</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3243,7 +3243,7 @@
         <v>126060370</v>
       </c>
       <c r="B26" t="n">
-        <v>98345</v>
+        <v>98349</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3340,7 +3340,7 @@
         <v>126060401</v>
       </c>
       <c r="B27" t="n">
-        <v>98345</v>
+        <v>98349</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3446,7 +3446,7 @@
         <v>126059838</v>
       </c>
       <c r="B28" t="n">
-        <v>78732</v>
+        <v>78736</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3543,7 +3543,7 @@
         <v>126057778</v>
       </c>
       <c r="B29" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3640,7 +3640,7 @@
         <v>126059586</v>
       </c>
       <c r="B30" t="n">
-        <v>98366</v>
+        <v>98370</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3737,7 +3737,7 @@
         <v>126058004</v>
       </c>
       <c r="B31" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3834,7 +3834,7 @@
         <v>126059336</v>
       </c>
       <c r="B32" t="n">
-        <v>98366</v>
+        <v>98370</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3931,7 +3931,7 @@
         <v>126059774</v>
       </c>
       <c r="B33" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4028,7 +4028,7 @@
         <v>126059386</v>
       </c>
       <c r="B34" t="n">
-        <v>80076</v>
+        <v>80080</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4125,7 +4125,7 @@
         <v>126059644</v>
       </c>
       <c r="B35" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4222,7 +4222,7 @@
         <v>126057983</v>
       </c>
       <c r="B36" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4319,7 +4319,7 @@
         <v>126057698</v>
       </c>
       <c r="B37" t="n">
-        <v>80076</v>
+        <v>80080</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4416,7 +4416,7 @@
         <v>126057797</v>
       </c>
       <c r="B38" t="n">
-        <v>98345</v>
+        <v>98349</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4522,7 +4522,7 @@
         <v>126059744</v>
       </c>
       <c r="B39" t="n">
-        <v>98345</v>
+        <v>98349</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4619,7 +4619,7 @@
         <v>126059357</v>
       </c>
       <c r="B40" t="n">
-        <v>98345</v>
+        <v>98349</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4722,54 +4722,45 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>126059509</v>
+        <v>126058294</v>
       </c>
       <c r="B41" t="n">
-        <v>98345</v>
+        <v>78977</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Kölsjöhållan, Kölsjöhållan, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>477425</v>
+        <v>477208</v>
       </c>
       <c r="R41" t="n">
-        <v>6847606</v>
+        <v>6847469</v>
       </c>
       <c r="S41" t="n">
         <v>15</v>
@@ -4828,10 +4819,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>126060437</v>
+        <v>126059509</v>
       </c>
       <c r="B42" t="n">
-        <v>98345</v>
+        <v>98349</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4858,7 +4849,7 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>130</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -4872,10 +4863,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>476993</v>
+        <v>477425</v>
       </c>
       <c r="R42" t="n">
-        <v>6847457</v>
+        <v>6847606</v>
       </c>
       <c r="S42" t="n">
         <v>15</v>
@@ -4934,45 +4925,54 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>126058294</v>
+        <v>126060437</v>
       </c>
       <c r="B43" t="n">
-        <v>78973</v>
+        <v>98349</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>130</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Kölsjöhållan, Kölsjöhållan, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>477208</v>
+        <v>476993</v>
       </c>
       <c r="R43" t="n">
-        <v>6847469</v>
+        <v>6847457</v>
       </c>
       <c r="S43" t="n">
         <v>15</v>

--- a/artfynd/A 31324-2024 artfynd.xlsx
+++ b/artfynd/A 31324-2024 artfynd.xlsx
@@ -3337,54 +3337,45 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>126060401</v>
+        <v>126059838</v>
       </c>
       <c r="B27" t="n">
-        <v>98349</v>
+        <v>78736</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Kölsjöhållan, Kölsjöhållan, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>477001</v>
+        <v>477260</v>
       </c>
       <c r="R27" t="n">
-        <v>6847471</v>
+        <v>6847508</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3443,45 +3434,54 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>126059838</v>
+        <v>126060401</v>
       </c>
       <c r="B28" t="n">
-        <v>78736</v>
+        <v>98349</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Kölsjöhållan, Kölsjöhållan, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>477260</v>
+        <v>477001</v>
       </c>
       <c r="R28" t="n">
-        <v>6847508</v>
+        <v>6847471</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3734,32 +3734,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>126058004</v>
+        <v>126059336</v>
       </c>
       <c r="B31" t="n">
-        <v>78977</v>
+        <v>98370</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3769,13 +3769,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>477074</v>
+        <v>477518</v>
       </c>
       <c r="R31" t="n">
-        <v>6847345</v>
+        <v>6847579</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3831,32 +3831,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>126059336</v>
+        <v>126058004</v>
       </c>
       <c r="B32" t="n">
-        <v>98370</v>
+        <v>78977</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3866,13 +3866,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>477518</v>
+        <v>477074</v>
       </c>
       <c r="R32" t="n">
-        <v>6847579</v>
+        <v>6847345</v>
       </c>
       <c r="S32" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>

--- a/artfynd/A 31324-2024 artfynd.xlsx
+++ b/artfynd/A 31324-2024 artfynd.xlsx
@@ -2924,7 +2924,7 @@
         <v>126060190</v>
       </c>
       <c r="B23" t="n">
-        <v>98349</v>
+        <v>98352</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3030,7 +3030,7 @@
         <v>126059672</v>
       </c>
       <c r="B24" t="n">
-        <v>98349</v>
+        <v>98352</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3243,7 +3243,7 @@
         <v>126060370</v>
       </c>
       <c r="B26" t="n">
-        <v>98349</v>
+        <v>98352</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3337,45 +3337,54 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>126059838</v>
+        <v>126060401</v>
       </c>
       <c r="B27" t="n">
-        <v>78736</v>
+        <v>98352</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Kölsjöhållan, Kölsjöhållan, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>477260</v>
+        <v>477001</v>
       </c>
       <c r="R27" t="n">
-        <v>6847508</v>
+        <v>6847471</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3434,54 +3443,45 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>126060401</v>
+        <v>126059838</v>
       </c>
       <c r="B28" t="n">
-        <v>98349</v>
+        <v>78736</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Kölsjöhållan, Kölsjöhållan, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>477001</v>
+        <v>477260</v>
       </c>
       <c r="R28" t="n">
-        <v>6847471</v>
+        <v>6847508</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3540,32 +3540,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126057778</v>
+        <v>126059586</v>
       </c>
       <c r="B29" t="n">
-        <v>78977</v>
+        <v>98373</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3575,13 +3575,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>476979</v>
+        <v>477373</v>
       </c>
       <c r="R29" t="n">
-        <v>6847356</v>
+        <v>6847629</v>
       </c>
       <c r="S29" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3637,32 +3637,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>126059586</v>
+        <v>126057778</v>
       </c>
       <c r="B30" t="n">
-        <v>98370</v>
+        <v>78977</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3672,13 +3672,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>477373</v>
+        <v>476979</v>
       </c>
       <c r="R30" t="n">
-        <v>6847629</v>
+        <v>6847356</v>
       </c>
       <c r="S30" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3734,32 +3734,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>126059336</v>
+        <v>126058004</v>
       </c>
       <c r="B31" t="n">
-        <v>98370</v>
+        <v>78977</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3769,13 +3769,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>477518</v>
+        <v>477074</v>
       </c>
       <c r="R31" t="n">
-        <v>6847579</v>
+        <v>6847345</v>
       </c>
       <c r="S31" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3831,32 +3831,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>126058004</v>
+        <v>126059336</v>
       </c>
       <c r="B32" t="n">
-        <v>78977</v>
+        <v>98373</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3866,13 +3866,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>477074</v>
+        <v>477518</v>
       </c>
       <c r="R32" t="n">
-        <v>6847345</v>
+        <v>6847579</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4416,7 +4416,7 @@
         <v>126057797</v>
       </c>
       <c r="B38" t="n">
-        <v>98349</v>
+        <v>98352</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4522,7 +4522,7 @@
         <v>126059744</v>
       </c>
       <c r="B39" t="n">
-        <v>98349</v>
+        <v>98352</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4619,7 +4619,7 @@
         <v>126059357</v>
       </c>
       <c r="B40" t="n">
-        <v>98349</v>
+        <v>98352</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4822,7 +4822,7 @@
         <v>126059509</v>
       </c>
       <c r="B42" t="n">
-        <v>98349</v>
+        <v>98352</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4928,7 +4928,7 @@
         <v>126060437</v>
       </c>
       <c r="B43" t="n">
-        <v>98349</v>
+        <v>98352</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>

--- a/artfynd/A 31324-2024 artfynd.xlsx
+++ b/artfynd/A 31324-2024 artfynd.xlsx
@@ -3540,32 +3540,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126059586</v>
+        <v>126057778</v>
       </c>
       <c r="B29" t="n">
-        <v>98373</v>
+        <v>78977</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3575,13 +3575,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>477373</v>
+        <v>476979</v>
       </c>
       <c r="R29" t="n">
-        <v>6847629</v>
+        <v>6847356</v>
       </c>
       <c r="S29" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3637,32 +3637,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>126057778</v>
+        <v>126059586</v>
       </c>
       <c r="B30" t="n">
-        <v>78977</v>
+        <v>98373</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3672,13 +3672,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>476979</v>
+        <v>477373</v>
       </c>
       <c r="R30" t="n">
-        <v>6847356</v>
+        <v>6847629</v>
       </c>
       <c r="S30" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>

--- a/artfynd/A 31324-2024 artfynd.xlsx
+++ b/artfynd/A 31324-2024 artfynd.xlsx
@@ -4122,7 +4122,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>126059644</v>
+        <v>126057983</v>
       </c>
       <c r="B35" t="n">
         <v>78977</v>
@@ -4157,10 +4157,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>477338</v>
+        <v>477073</v>
       </c>
       <c r="R35" t="n">
-        <v>6847624</v>
+        <v>6847347</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>
@@ -4219,7 +4219,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>126057983</v>
+        <v>126059644</v>
       </c>
       <c r="B36" t="n">
         <v>78977</v>
@@ -4254,10 +4254,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>477073</v>
+        <v>477338</v>
       </c>
       <c r="R36" t="n">
-        <v>6847347</v>
+        <v>6847624</v>
       </c>
       <c r="S36" t="n">
         <v>15</v>

--- a/artfynd/A 31324-2024 artfynd.xlsx
+++ b/artfynd/A 31324-2024 artfynd.xlsx
@@ -3734,32 +3734,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>126058004</v>
+        <v>126059336</v>
       </c>
       <c r="B31" t="n">
-        <v>78977</v>
+        <v>98373</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3769,13 +3769,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>477074</v>
+        <v>477518</v>
       </c>
       <c r="R31" t="n">
-        <v>6847345</v>
+        <v>6847579</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3831,32 +3831,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>126059336</v>
+        <v>126058004</v>
       </c>
       <c r="B32" t="n">
-        <v>98373</v>
+        <v>78977</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3866,13 +3866,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>477518</v>
+        <v>477074</v>
       </c>
       <c r="R32" t="n">
-        <v>6847579</v>
+        <v>6847345</v>
       </c>
       <c r="S32" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4122,7 +4122,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>126057983</v>
+        <v>126059644</v>
       </c>
       <c r="B35" t="n">
         <v>78977</v>
@@ -4157,10 +4157,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>477073</v>
+        <v>477338</v>
       </c>
       <c r="R35" t="n">
-        <v>6847347</v>
+        <v>6847624</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>
@@ -4219,7 +4219,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>126059644</v>
+        <v>126057983</v>
       </c>
       <c r="B36" t="n">
         <v>78977</v>
@@ -4254,10 +4254,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>477338</v>
+        <v>477073</v>
       </c>
       <c r="R36" t="n">
-        <v>6847624</v>
+        <v>6847347</v>
       </c>
       <c r="S36" t="n">
         <v>15</v>

--- a/artfynd/A 31324-2024 artfynd.xlsx
+++ b/artfynd/A 31324-2024 artfynd.xlsx
@@ -2924,7 +2924,7 @@
         <v>126060190</v>
       </c>
       <c r="B23" t="n">
-        <v>98352</v>
+        <v>98361</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3030,7 +3030,7 @@
         <v>126059672</v>
       </c>
       <c r="B24" t="n">
-        <v>98352</v>
+        <v>98361</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3136,7 +3136,7 @@
         <v>126060256</v>
       </c>
       <c r="B25" t="n">
-        <v>56848</v>
+        <v>56849</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3243,7 +3243,7 @@
         <v>126060370</v>
       </c>
       <c r="B26" t="n">
-        <v>98352</v>
+        <v>98361</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3340,7 +3340,7 @@
         <v>126060401</v>
       </c>
       <c r="B27" t="n">
-        <v>98352</v>
+        <v>98361</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3446,7 +3446,7 @@
         <v>126059838</v>
       </c>
       <c r="B28" t="n">
-        <v>78736</v>
+        <v>78739</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3543,7 +3543,7 @@
         <v>126057778</v>
       </c>
       <c r="B29" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3640,7 +3640,7 @@
         <v>126059586</v>
       </c>
       <c r="B30" t="n">
-        <v>98373</v>
+        <v>98382</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3734,32 +3734,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>126059336</v>
+        <v>126058004</v>
       </c>
       <c r="B31" t="n">
-        <v>98373</v>
+        <v>78980</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3769,13 +3769,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>477518</v>
+        <v>477074</v>
       </c>
       <c r="R31" t="n">
-        <v>6847579</v>
+        <v>6847345</v>
       </c>
       <c r="S31" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3831,32 +3831,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>126058004</v>
+        <v>126059336</v>
       </c>
       <c r="B32" t="n">
-        <v>78977</v>
+        <v>98382</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3866,13 +3866,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>477074</v>
+        <v>477518</v>
       </c>
       <c r="R32" t="n">
-        <v>6847345</v>
+        <v>6847579</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3931,7 +3931,7 @@
         <v>126059774</v>
       </c>
       <c r="B33" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4028,7 +4028,7 @@
         <v>126059386</v>
       </c>
       <c r="B34" t="n">
-        <v>80080</v>
+        <v>80083</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4125,7 +4125,7 @@
         <v>126059644</v>
       </c>
       <c r="B35" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4222,7 +4222,7 @@
         <v>126057983</v>
       </c>
       <c r="B36" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4319,7 +4319,7 @@
         <v>126057698</v>
       </c>
       <c r="B37" t="n">
-        <v>80080</v>
+        <v>80083</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4416,7 +4416,7 @@
         <v>126057797</v>
       </c>
       <c r="B38" t="n">
-        <v>98352</v>
+        <v>98361</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4522,7 +4522,7 @@
         <v>126059744</v>
       </c>
       <c r="B39" t="n">
-        <v>98352</v>
+        <v>98361</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4619,7 +4619,7 @@
         <v>126059357</v>
       </c>
       <c r="B40" t="n">
-        <v>98352</v>
+        <v>98361</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4725,7 +4725,7 @@
         <v>126058294</v>
       </c>
       <c r="B41" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4822,7 +4822,7 @@
         <v>126059509</v>
       </c>
       <c r="B42" t="n">
-        <v>98352</v>
+        <v>98361</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4928,7 +4928,7 @@
         <v>126060437</v>
       </c>
       <c r="B43" t="n">
-        <v>98352</v>
+        <v>98361</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>

--- a/artfynd/A 31324-2024 artfynd.xlsx
+++ b/artfynd/A 31324-2024 artfynd.xlsx
@@ -4722,45 +4722,54 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>126058294</v>
+        <v>126059509</v>
       </c>
       <c r="B41" t="n">
-        <v>78980</v>
+        <v>98361</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Kölsjöhållan, Kölsjöhållan, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>477208</v>
+        <v>477425</v>
       </c>
       <c r="R41" t="n">
-        <v>6847469</v>
+        <v>6847606</v>
       </c>
       <c r="S41" t="n">
         <v>15</v>
@@ -4819,7 +4828,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>126059509</v>
+        <v>126060437</v>
       </c>
       <c r="B42" t="n">
         <v>98361</v>
@@ -4849,7 +4858,7 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>130</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -4863,10 +4872,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>477425</v>
+        <v>476993</v>
       </c>
       <c r="R42" t="n">
-        <v>6847606</v>
+        <v>6847457</v>
       </c>
       <c r="S42" t="n">
         <v>15</v>
@@ -4925,54 +4934,45 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>126060437</v>
+        <v>126058294</v>
       </c>
       <c r="B43" t="n">
-        <v>98361</v>
+        <v>78980</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>130</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Kölsjöhållan, Kölsjöhållan, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>476993</v>
+        <v>477208</v>
       </c>
       <c r="R43" t="n">
-        <v>6847457</v>
+        <v>6847469</v>
       </c>
       <c r="S43" t="n">
         <v>15</v>

--- a/artfynd/A 31324-2024 artfynd.xlsx
+++ b/artfynd/A 31324-2024 artfynd.xlsx
@@ -4025,10 +4025,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>126059386</v>
+        <v>126059644</v>
       </c>
       <c r="B34" t="n">
-        <v>80083</v>
+        <v>78980</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4036,21 +4036,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4060,10 +4060,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>477486</v>
+        <v>477338</v>
       </c>
       <c r="R34" t="n">
-        <v>6847598</v>
+        <v>6847624</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -4122,10 +4122,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>126059644</v>
+        <v>126059386</v>
       </c>
       <c r="B35" t="n">
-        <v>78980</v>
+        <v>80083</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4133,21 +4133,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4157,10 +4157,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>477338</v>
+        <v>477486</v>
       </c>
       <c r="R35" t="n">
-        <v>6847624</v>
+        <v>6847598</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>
@@ -4722,54 +4722,45 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>126059509</v>
+        <v>126058294</v>
       </c>
       <c r="B41" t="n">
-        <v>98361</v>
+        <v>78980</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Kölsjöhållan, Kölsjöhållan, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>477425</v>
+        <v>477208</v>
       </c>
       <c r="R41" t="n">
-        <v>6847606</v>
+        <v>6847469</v>
       </c>
       <c r="S41" t="n">
         <v>15</v>
@@ -4828,7 +4819,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>126060437</v>
+        <v>126059509</v>
       </c>
       <c r="B42" t="n">
         <v>98361</v>
@@ -4858,7 +4849,7 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>130</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -4872,10 +4863,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>476993</v>
+        <v>477425</v>
       </c>
       <c r="R42" t="n">
-        <v>6847457</v>
+        <v>6847606</v>
       </c>
       <c r="S42" t="n">
         <v>15</v>
@@ -4934,45 +4925,54 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>126058294</v>
+        <v>126060437</v>
       </c>
       <c r="B43" t="n">
-        <v>78980</v>
+        <v>98361</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>130</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Kölsjöhållan, Kölsjöhållan, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>477208</v>
+        <v>476993</v>
       </c>
       <c r="R43" t="n">
-        <v>6847469</v>
+        <v>6847457</v>
       </c>
       <c r="S43" t="n">
         <v>15</v>

--- a/artfynd/A 31324-2024 artfynd.xlsx
+++ b/artfynd/A 31324-2024 artfynd.xlsx
@@ -3734,32 +3734,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>126058004</v>
+        <v>126059336</v>
       </c>
       <c r="B31" t="n">
-        <v>78980</v>
+        <v>98382</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3769,13 +3769,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>477074</v>
+        <v>477518</v>
       </c>
       <c r="R31" t="n">
-        <v>6847345</v>
+        <v>6847579</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3831,32 +3831,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>126059336</v>
+        <v>126058004</v>
       </c>
       <c r="B32" t="n">
-        <v>98382</v>
+        <v>78980</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3866,13 +3866,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>477518</v>
+        <v>477074</v>
       </c>
       <c r="R32" t="n">
-        <v>6847579</v>
+        <v>6847345</v>
       </c>
       <c r="S32" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>

--- a/artfynd/A 31324-2024 artfynd.xlsx
+++ b/artfynd/A 31324-2024 artfynd.xlsx
@@ -3734,32 +3734,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>126059336</v>
+        <v>126058004</v>
       </c>
       <c r="B31" t="n">
-        <v>98382</v>
+        <v>78980</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3769,13 +3769,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>477518</v>
+        <v>477074</v>
       </c>
       <c r="R31" t="n">
-        <v>6847579</v>
+        <v>6847345</v>
       </c>
       <c r="S31" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3831,32 +3831,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>126058004</v>
+        <v>126059336</v>
       </c>
       <c r="B32" t="n">
-        <v>78980</v>
+        <v>98382</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3866,13 +3866,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>477074</v>
+        <v>477518</v>
       </c>
       <c r="R32" t="n">
-        <v>6847345</v>
+        <v>6847579</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>

--- a/artfynd/A 31324-2024 artfynd.xlsx
+++ b/artfynd/A 31324-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY43"/>
+  <dimension ref="A1:AY44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,16 +678,11 @@
         <v>118676032</v>
       </c>
       <c r="B2" t="n">
-        <v>91791</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -786,57 +781,48 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118676034</v>
+        <v>123771759</v>
       </c>
       <c r="B3" t="n">
-        <v>78229</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Fågelsjö, Dlr</t>
+          <t>Kölsjöhållan, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>477241</v>
+        <v>477096</v>
       </c>
       <c r="R3" t="n">
-        <v>6847418</v>
+        <v>6847397</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -860,17 +846,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-05-30</t>
+          <t>2024-07-26</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-05-30</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>2024-07-26</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -885,31 +866,30 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Gabriella Fjordmark Lerne</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr"/>
+          <t>Gabriella Fjordmark Lerne</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2024 Fågelsjö</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123771759</v>
+        <v>123771760</v>
       </c>
       <c r="B4" t="n">
-        <v>78810</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -937,10 +917,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>477096</v>
+        <v>477028</v>
       </c>
       <c r="R4" t="n">
-        <v>6847397</v>
+        <v>6847394</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -1003,15 +983,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123771745</v>
+        <v>126057778</v>
       </c>
       <c r="B5" t="n">
-        <v>98101</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1019,34 +994,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Kölsjöhållan, Dlr</t>
+          <t>Kölsjöhållan, Kölsjöhållan, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>477255</v>
+        <v>476979</v>
       </c>
       <c r="R5" t="n">
-        <v>6847445</v>
+        <v>6847356</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1073,12 +1048,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-07-26</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-07-26</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1093,31 +1068,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Gabriella Fjordmark Lerne</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Gabriella Fjordmark Lerne</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr">
-        <is>
-          <t>Forskningsresan i Naturvårdens Utmarker 2024 Fågelsjö</t>
-        </is>
-      </c>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123771747</v>
+        <v>126057983</v>
       </c>
       <c r="B6" t="n">
-        <v>98101</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1125,34 +1091,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Kölsjöhållan, Dlr</t>
+          <t>Kölsjöhållan, Kölsjöhållan, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>477134</v>
+        <v>477073</v>
       </c>
       <c r="R6" t="n">
-        <v>6847450</v>
+        <v>6847347</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1179,12 +1145,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-07-26</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-07-26</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1199,31 +1165,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Gabriella Fjordmark Lerne</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Gabriella Fjordmark Lerne</t>
-        </is>
-      </c>
-      <c r="AY6" t="inlineStr">
-        <is>
-          <t>Forskningsresan i Naturvårdens Utmarker 2024 Fågelsjö</t>
-        </is>
-      </c>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123771744</v>
+        <v>126058004</v>
       </c>
       <c r="B7" t="n">
-        <v>98101</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1231,37 +1188,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Kölsjöhållan, Dlr</t>
+          <t>Kölsjöhållan, Kölsjöhållan, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>477281</v>
+        <v>477074</v>
       </c>
       <c r="R7" t="n">
-        <v>6847618</v>
+        <v>6847345</v>
       </c>
       <c r="S7" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1285,12 +1242,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-07-26</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-07-26</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1305,31 +1262,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Gabriella Fjordmark Lerne</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Gabriella Fjordmark Lerne</t>
-        </is>
-      </c>
-      <c r="AY7" t="inlineStr">
-        <is>
-          <t>Forskningsresan i Naturvårdens Utmarker 2024 Fågelsjö</t>
-        </is>
-      </c>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123771746</v>
+        <v>126058294</v>
       </c>
       <c r="B8" t="n">
-        <v>98101</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1337,34 +1285,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Kölsjöhållan, Dlr</t>
+          <t>Kölsjöhållan, Kölsjöhållan, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>477174</v>
+        <v>477208</v>
       </c>
       <c r="R8" t="n">
-        <v>6847450</v>
+        <v>6847469</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1391,12 +1339,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-07-26</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-07-26</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1411,31 +1359,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Gabriella Fjordmark Lerne</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Gabriella Fjordmark Lerne</t>
-        </is>
-      </c>
-      <c r="AY8" t="inlineStr">
-        <is>
-          <t>Forskningsresan i Naturvårdens Utmarker 2024 Fågelsjö</t>
-        </is>
-      </c>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123771756</v>
+        <v>126059644</v>
       </c>
       <c r="B9" t="n">
-        <v>98101</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1443,34 +1382,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Kölsjöhållan, Dlr</t>
+          <t>Kölsjöhållan, Kölsjöhållan, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>476937</v>
+        <v>477338</v>
       </c>
       <c r="R9" t="n">
-        <v>6847291</v>
+        <v>6847624</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1497,17 +1436,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2024-07-26</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2024-07-26</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Minst 100 många i blom</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1522,35 +1456,26 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Gabriella Fjordmark Lerne</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Gabriella Fjordmark Lerne</t>
-        </is>
-      </c>
-      <c r="AY9" t="inlineStr">
-        <is>
-          <t>Forskningsresan i Naturvårdens Utmarker 2024 Fågelsjö</t>
-        </is>
-      </c>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123771760</v>
+        <v>126059774</v>
       </c>
       <c r="B10" t="n">
-        <v>78810</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
@@ -1574,17 +1499,17 @@
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Kölsjöhållan, Dlr</t>
+          <t>Kölsjöhållan, Kölsjöhållan, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>477028</v>
+        <v>477317</v>
       </c>
       <c r="R10" t="n">
-        <v>6847394</v>
+        <v>6847536</v>
       </c>
       <c r="S10" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1608,12 +1533,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2024-07-26</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2024-07-26</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1628,69 +1553,64 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Gabriella Fjordmark Lerne</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Gabriella Fjordmark Lerne</t>
-        </is>
-      </c>
-      <c r="AY10" t="inlineStr">
-        <is>
-          <t>Forskningsresan i Naturvårdens Utmarker 2024 Fågelsjö</t>
-        </is>
-      </c>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123771763</v>
+        <v>118676034</v>
       </c>
       <c r="B11" t="n">
-        <v>98018</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79084</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>219790</v>
+        <v>6446</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Kölsjöhållan, Dlr</t>
+          <t>Fågelsjö, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>476949</v>
+        <v>477241</v>
       </c>
       <c r="R11" t="n">
-        <v>6847393</v>
+        <v>6847418</v>
       </c>
       <c r="S11" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1714,12 +1634,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2024-07-26</t>
+          <t>2024-05-30</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2024-07-26</t>
+          <t>2024-05-30</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1734,53 +1659,44 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Gabriella Fjordmark Lerne</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Gabriella Fjordmark Lerne</t>
-        </is>
-      </c>
-      <c r="AY11" t="inlineStr">
-        <is>
-          <t>Forskningsresan i Naturvårdens Utmarker 2024 Fågelsjö</t>
-        </is>
-      </c>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123771750</v>
+        <v>123771718</v>
       </c>
       <c r="B12" t="n">
-        <v>98101</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1790,10 +1706,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>477093</v>
+        <v>477293</v>
       </c>
       <c r="R12" t="n">
-        <v>6847398</v>
+        <v>6847591</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1856,50 +1772,45 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123771749</v>
+        <v>126057698</v>
       </c>
       <c r="B13" t="n">
-        <v>98101</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Kölsjöhållan, Dlr</t>
+          <t>Kölsjöhållan, Kölsjöhållan, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>477122</v>
+        <v>476959</v>
       </c>
       <c r="R13" t="n">
-        <v>6847410</v>
+        <v>6847356</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1926,12 +1837,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2024-07-26</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2024-07-26</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1946,31 +1857,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Gabriella Fjordmark Lerne</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Gabriella Fjordmark Lerne</t>
-        </is>
-      </c>
-      <c r="AY13" t="inlineStr">
-        <is>
-          <t>Forskningsresan i Naturvårdens Utmarker 2024 Fågelsjö</t>
-        </is>
-      </c>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123771718</v>
+        <v>126059386</v>
       </c>
       <c r="B14" t="n">
-        <v>79428</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1978,34 +1880,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6453</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Kölsjöhållan, Dlr</t>
+          <t>Kölsjöhållan, Kölsjöhållan, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>477293</v>
+        <v>477486</v>
       </c>
       <c r="R14" t="n">
-        <v>6847591</v>
+        <v>6847598</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2032,12 +1934,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2024-07-26</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2024-07-26</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2052,53 +1954,44 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Gabriella Fjordmark Lerne</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Gabriella Fjordmark Lerne</t>
-        </is>
-      </c>
-      <c r="AY14" t="inlineStr">
-        <is>
-          <t>Forskningsresan i Naturvårdens Utmarker 2024 Fågelsjö</t>
-        </is>
-      </c>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123771754</v>
+        <v>123771732</v>
       </c>
       <c r="B15" t="n">
-        <v>98101</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80460</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>6461</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2108,10 +2001,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>476918</v>
+        <v>477018</v>
       </c>
       <c r="R15" t="n">
-        <v>6847369</v>
+        <v>6847382</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2174,50 +2067,55 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123771752</v>
+        <v>126060256</v>
       </c>
       <c r="B16" t="n">
-        <v>98101</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Kölsjöhållan, Dlr</t>
+          <t>Kölsjöhållan, Kölsjöhållan, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>477001</v>
+        <v>477022</v>
       </c>
       <c r="R16" t="n">
-        <v>6847417</v>
+        <v>6847543</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2244,12 +2142,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2024-07-26</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2024-07-26</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2264,53 +2162,44 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Gabriella Fjordmark Lerne</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Gabriella Fjordmark Lerne</t>
-        </is>
-      </c>
-      <c r="AY16" t="inlineStr">
-        <is>
-          <t>Forskningsresan i Naturvårdens Utmarker 2024 Fågelsjö</t>
-        </is>
-      </c>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123771748</v>
+        <v>123771762</v>
       </c>
       <c r="B17" t="n">
-        <v>98101</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99035</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2320,10 +2209,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>477135</v>
+        <v>477280</v>
       </c>
       <c r="R17" t="n">
-        <v>6847443</v>
+        <v>6847646</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2386,37 +2275,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123771757</v>
+        <v>123771763</v>
       </c>
       <c r="B18" t="n">
-        <v>98101</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99035</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2426,10 +2310,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>476911</v>
+        <v>476949</v>
       </c>
       <c r="R18" t="n">
-        <v>6847329</v>
+        <v>6847393</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2492,37 +2376,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123771733</v>
+        <v>123771744</v>
       </c>
       <c r="B19" t="n">
-        <v>78547</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2532,10 +2411,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>477300</v>
+        <v>477281</v>
       </c>
       <c r="R19" t="n">
-        <v>6847594</v>
+        <v>6847618</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2598,37 +2477,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123771732</v>
+        <v>123771745</v>
       </c>
       <c r="B20" t="n">
-        <v>79919</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6461</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2638,10 +2512,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>477018</v>
+        <v>477255</v>
       </c>
       <c r="R20" t="n">
-        <v>6847382</v>
+        <v>6847445</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2704,15 +2578,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123771751</v>
+        <v>123771746</v>
       </c>
       <c r="B21" t="n">
-        <v>98101</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2744,10 +2613,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>477034</v>
+        <v>477174</v>
       </c>
       <c r="R21" t="n">
-        <v>6847389</v>
+        <v>6847450</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2810,15 +2679,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123771753</v>
+        <v>123771747</v>
       </c>
       <c r="B22" t="n">
-        <v>98101</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2850,10 +2714,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>476964</v>
+        <v>477134</v>
       </c>
       <c r="R22" t="n">
-        <v>6847387</v>
+        <v>6847450</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2886,11 +2750,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2024-07-26</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Blomning över 80 stänglar</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2921,10 +2780,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>126060190</v>
+        <v>123771748</v>
       </c>
       <c r="B23" t="n">
-        <v>98361</v>
+        <v>99118</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2949,26 +2808,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>90</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Kölsjöhållan, Kölsjöhållan, Dlr</t>
+          <t>Kölsjöhållan, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>477091</v>
+        <v>477135</v>
       </c>
       <c r="R23" t="n">
-        <v>6847536</v>
+        <v>6847443</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -2995,12 +2845,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2024-07-26</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2024-07-26</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3015,22 +2865,26 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Gabriella Fjordmark Lerne</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
-        </is>
-      </c>
-      <c r="AY23" t="inlineStr"/>
+          <t>Gabriella Fjordmark Lerne</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2024 Fågelsjö</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>126059672</v>
+        <v>123771749</v>
       </c>
       <c r="B24" t="n">
-        <v>98361</v>
+        <v>99118</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3055,26 +2909,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Kölsjöhållan, Kölsjöhållan, Dlr</t>
+          <t>Kölsjöhållan, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>477334</v>
+        <v>477122</v>
       </c>
       <c r="R24" t="n">
-        <v>6847619</v>
+        <v>6847410</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -3101,12 +2946,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2024-07-26</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2024-07-26</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3121,67 +2966,61 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Gabriella Fjordmark Lerne</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
-        </is>
-      </c>
-      <c r="AY24" t="inlineStr"/>
+          <t>Gabriella Fjordmark Lerne</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2024 Fågelsjö</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>126060256</v>
+        <v>123771750</v>
       </c>
       <c r="B25" t="n">
-        <v>56849</v>
+        <v>99118</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L25" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Kölsjöhållan, Kölsjöhållan, Dlr</t>
+          <t>Kölsjöhållan, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>477022</v>
+        <v>477093</v>
       </c>
       <c r="R25" t="n">
-        <v>6847543</v>
+        <v>6847398</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3208,12 +3047,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2024-07-26</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2024-07-26</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3228,22 +3067,26 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Gabriella Fjordmark Lerne</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
-        </is>
-      </c>
-      <c r="AY25" t="inlineStr"/>
+          <t>Gabriella Fjordmark Lerne</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2024 Fågelsjö</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>126060370</v>
+        <v>123771751</v>
       </c>
       <c r="B26" t="n">
-        <v>98361</v>
+        <v>99118</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3271,14 +3114,14 @@
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Kölsjöhållan, Kölsjöhållan, Dlr</t>
+          <t>Kölsjöhållan, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>477008</v>
+        <v>477034</v>
       </c>
       <c r="R26" t="n">
-        <v>6847504</v>
+        <v>6847389</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3305,12 +3148,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2024-07-26</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2024-07-26</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3325,22 +3168,26 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Gabriella Fjordmark Lerne</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
-        </is>
-      </c>
-      <c r="AY26" t="inlineStr"/>
+          <t>Gabriella Fjordmark Lerne</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2024 Fågelsjö</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>126060401</v>
+        <v>123771752</v>
       </c>
       <c r="B27" t="n">
-        <v>98361</v>
+        <v>99118</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3365,29 +3212,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Kölsjöhållan, Kölsjöhållan, Dlr</t>
+          <t>Kölsjöhållan, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
         <v>477001</v>
       </c>
       <c r="R27" t="n">
-        <v>6847471</v>
+        <v>6847417</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3411,12 +3249,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2024-07-26</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2024-07-26</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3431,60 +3269,64 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Gabriella Fjordmark Lerne</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
-        </is>
-      </c>
-      <c r="AY27" t="inlineStr"/>
+          <t>Gabriella Fjordmark Lerne</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2024 Fågelsjö</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>126059838</v>
+        <v>123771753</v>
       </c>
       <c r="B28" t="n">
-        <v>78739</v>
+        <v>99118</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Kölsjöhållan, Kölsjöhållan, Dlr</t>
+          <t>Kölsjöhållan, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>477260</v>
+        <v>476964</v>
       </c>
       <c r="R28" t="n">
-        <v>6847508</v>
+        <v>6847387</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3508,12 +3350,17 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2024-07-26</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2024-07-26</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Blomning över 80 stänglar</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3528,57 +3375,61 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Gabriella Fjordmark Lerne</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
-        </is>
-      </c>
-      <c r="AY28" t="inlineStr"/>
+          <t>Gabriella Fjordmark Lerne</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2024 Fågelsjö</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126057778</v>
+        <v>123771754</v>
       </c>
       <c r="B29" t="n">
-        <v>78980</v>
+        <v>99118</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Kölsjöhållan, Kölsjöhållan, Dlr</t>
+          <t>Kölsjöhållan, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>476979</v>
+        <v>476918</v>
       </c>
       <c r="R29" t="n">
-        <v>6847356</v>
+        <v>6847369</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3605,12 +3456,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2024-07-26</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2024-07-26</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3625,60 +3476,64 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Gabriella Fjordmark Lerne</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
-        </is>
-      </c>
-      <c r="AY29" t="inlineStr"/>
+          <t>Gabriella Fjordmark Lerne</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2024 Fågelsjö</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>126059586</v>
+        <v>123771756</v>
       </c>
       <c r="B30" t="n">
-        <v>98382</v>
+        <v>99118</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Kölsjöhållan, Kölsjöhållan, Dlr</t>
+          <t>Kölsjöhållan, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>477373</v>
+        <v>476937</v>
       </c>
       <c r="R30" t="n">
-        <v>6847629</v>
+        <v>6847291</v>
       </c>
       <c r="S30" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3702,12 +3557,17 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2024-07-26</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2024-07-26</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Minst 100 många i blom</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3722,60 +3582,64 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Gabriella Fjordmark Lerne</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
-        </is>
-      </c>
-      <c r="AY30" t="inlineStr"/>
+          <t>Gabriella Fjordmark Lerne</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2024 Fågelsjö</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>126058004</v>
+        <v>123771757</v>
       </c>
       <c r="B31" t="n">
-        <v>78980</v>
+        <v>99118</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Kölsjöhållan, Kölsjöhållan, Dlr</t>
+          <t>Kölsjöhållan, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>477074</v>
+        <v>476911</v>
       </c>
       <c r="R31" t="n">
-        <v>6847345</v>
+        <v>6847329</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3799,12 +3663,12 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2024-07-26</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2024-07-26</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3819,57 +3683,70 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Gabriella Fjordmark Lerne</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
-        </is>
-      </c>
-      <c r="AY31" t="inlineStr"/>
+          <t>Gabriella Fjordmark Lerne</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2024 Fågelsjö</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>126059336</v>
+        <v>126057797</v>
       </c>
       <c r="B32" t="n">
-        <v>98382</v>
+        <v>99118</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Kölsjöhållan, Kölsjöhållan, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>477518</v>
+        <v>476979</v>
       </c>
       <c r="R32" t="n">
-        <v>6847579</v>
+        <v>6847360</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -3928,48 +3805,57 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>126059774</v>
+        <v>126059357</v>
       </c>
       <c r="B33" t="n">
-        <v>78980</v>
+        <v>99118</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Kölsjöhållan, Kölsjöhållan, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>477317</v>
+        <v>477503</v>
       </c>
       <c r="R33" t="n">
-        <v>6847536</v>
+        <v>6847581</v>
       </c>
       <c r="S33" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4025,45 +3911,54 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>126059644</v>
+        <v>126059509</v>
       </c>
       <c r="B34" t="n">
-        <v>78980</v>
+        <v>99118</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Kölsjöhållan, Kölsjöhållan, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>477338</v>
+        <v>477425</v>
       </c>
       <c r="R34" t="n">
-        <v>6847624</v>
+        <v>6847606</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -4122,45 +4017,54 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>126059386</v>
+        <v>126059672</v>
       </c>
       <c r="B35" t="n">
-        <v>80083</v>
+        <v>99118</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Kölsjöhållan, Kölsjöhållan, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>477486</v>
+        <v>477334</v>
       </c>
       <c r="R35" t="n">
-        <v>6847598</v>
+        <v>6847619</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>
@@ -4219,32 +4123,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>126057983</v>
+        <v>126059744</v>
       </c>
       <c r="B36" t="n">
-        <v>78980</v>
+        <v>99118</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4254,10 +4158,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>477073</v>
+        <v>477337</v>
       </c>
       <c r="R36" t="n">
-        <v>6847347</v>
+        <v>6847567</v>
       </c>
       <c r="S36" t="n">
         <v>15</v>
@@ -4316,45 +4220,54 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>126057698</v>
+        <v>126060190</v>
       </c>
       <c r="B37" t="n">
-        <v>80083</v>
+        <v>99118</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Kölsjöhållan, Kölsjöhållan, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>476959</v>
+        <v>477091</v>
       </c>
       <c r="R37" t="n">
-        <v>6847356</v>
+        <v>6847536</v>
       </c>
       <c r="S37" t="n">
         <v>15</v>
@@ -4413,10 +4326,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>126057797</v>
+        <v>126060370</v>
       </c>
       <c r="B38" t="n">
-        <v>98361</v>
+        <v>99118</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4441,26 +4354,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Kölsjöhållan, Kölsjöhållan, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>476979</v>
+        <v>477008</v>
       </c>
       <c r="R38" t="n">
-        <v>6847360</v>
+        <v>6847504</v>
       </c>
       <c r="S38" t="n">
         <v>15</v>
@@ -4519,10 +4423,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>126059744</v>
+        <v>126060401</v>
       </c>
       <c r="B39" t="n">
-        <v>98361</v>
+        <v>99118</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4547,20 +4451,29 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I39" t="inlineStr"/>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Kölsjöhållan, Kölsjöhållan, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>477337</v>
+        <v>477001</v>
       </c>
       <c r="R39" t="n">
-        <v>6847567</v>
+        <v>6847471</v>
       </c>
       <c r="S39" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4616,10 +4529,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>126059357</v>
+        <v>126060437</v>
       </c>
       <c r="B40" t="n">
-        <v>98361</v>
+        <v>99118</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4646,7 +4559,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>130</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -4660,10 +4573,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>477503</v>
+        <v>476993</v>
       </c>
       <c r="R40" t="n">
-        <v>6847581</v>
+        <v>6847457</v>
       </c>
       <c r="S40" t="n">
         <v>15</v>
@@ -4722,54 +4635,45 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>126059509</v>
+        <v>126059336</v>
       </c>
       <c r="B41" t="n">
-        <v>98361</v>
+        <v>99140</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>220787</v>
+        <v>221952</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Kölsjöhållan, Kölsjöhållan, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>477425</v>
+        <v>477518</v>
       </c>
       <c r="R41" t="n">
-        <v>6847606</v>
+        <v>6847579</v>
       </c>
       <c r="S41" t="n">
         <v>15</v>
@@ -4828,57 +4732,48 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>126060437</v>
+        <v>126059586</v>
       </c>
       <c r="B42" t="n">
-        <v>98361</v>
+        <v>99140</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>220787</v>
+        <v>221952</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>130</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Kölsjöhållan, Kölsjöhållan, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>476993</v>
+        <v>477373</v>
       </c>
       <c r="R42" t="n">
-        <v>6847457</v>
+        <v>6847629</v>
       </c>
       <c r="S42" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -4934,10 +4829,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>126058294</v>
+        <v>123771733</v>
       </c>
       <c r="B43" t="n">
-        <v>78980</v>
+        <v>79085</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4945,34 +4840,34 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Kölsjöhållan, Kölsjöhållan, Dlr</t>
+          <t>Kölsjöhållan, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>477208</v>
+        <v>477300</v>
       </c>
       <c r="R43" t="n">
-        <v>6847469</v>
+        <v>6847594</v>
       </c>
       <c r="S43" t="n">
         <v>15</v>
@@ -4999,12 +4894,12 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2024-07-26</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2024-07-26</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5019,15 +4914,116 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
+          <t>Gabriella Fjordmark Lerne</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Gabriella Fjordmark Lerne</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2024 Fågelsjö</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>126059838</v>
+      </c>
+      <c r="B44" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Kölsjöhållan, Kölsjöhållan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>477260</v>
+      </c>
+      <c r="R44" t="n">
+        <v>6847508</v>
+      </c>
+      <c r="S44" t="n">
+        <v>10</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
           <t>Anders Heggestad</t>
         </is>
       </c>
-      <c r="AX43" t="inlineStr">
+      <c r="AX44" t="inlineStr">
         <is>
           <t>Anders Heggestad</t>
         </is>
       </c>
-      <c r="AY43" t="inlineStr"/>
+      <c r="AY44" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 31324-2024 artfynd.xlsx
+++ b/artfynd/A 31324-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY44"/>
+  <dimension ref="A1:AZ44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -778,6 +783,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118676032</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -879,6 +889,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2024 Fågelsjö</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123771759</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -980,6 +995,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2024 Fågelsjö</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123771760</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1077,6 +1097,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126057778</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1174,6 +1199,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126057983</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1271,6 +1301,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126058004</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1368,6 +1403,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126058294</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1465,6 +1505,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126059644</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1562,6 +1607,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126059774</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1668,6 +1718,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118676034</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1769,6 +1824,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2024 Fågelsjö</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123771718</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1866,6 +1926,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126057698</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1963,6 +2028,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126059386</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2064,6 +2134,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2024 Fågelsjö</t>
         </is>
       </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123771732</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2171,6 +2246,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126060256</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2272,6 +2352,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2024 Fågelsjö</t>
         </is>
       </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123771762</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2373,6 +2458,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2024 Fågelsjö</t>
         </is>
       </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123771763</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2474,6 +2564,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2024 Fågelsjö</t>
         </is>
       </c>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123771744</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2575,6 +2670,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2024 Fågelsjö</t>
         </is>
       </c>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123771745</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2676,6 +2776,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2024 Fågelsjö</t>
         </is>
       </c>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123771746</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2777,6 +2882,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2024 Fågelsjö</t>
         </is>
       </c>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123771747</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2878,6 +2988,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2024 Fågelsjö</t>
         </is>
       </c>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123771748</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2979,6 +3094,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2024 Fågelsjö</t>
         </is>
       </c>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123771749</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3080,6 +3200,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2024 Fågelsjö</t>
         </is>
       </c>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123771750</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3181,6 +3306,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2024 Fågelsjö</t>
         </is>
       </c>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123771751</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3282,6 +3412,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2024 Fågelsjö</t>
         </is>
       </c>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123771752</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3388,6 +3523,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2024 Fågelsjö</t>
         </is>
       </c>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123771753</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3489,6 +3629,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2024 Fågelsjö</t>
         </is>
       </c>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123771754</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3595,6 +3740,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2024 Fågelsjö</t>
         </is>
       </c>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123771756</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3696,6 +3846,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2024 Fågelsjö</t>
         </is>
       </c>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123771757</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3802,6 +3957,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126057797</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3908,6 +4068,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126059357</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4014,6 +4179,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126059509</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4120,6 +4290,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126059672</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4217,6 +4392,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126059744</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4323,6 +4503,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126060190</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4420,6 +4605,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126060370</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4526,6 +4716,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126060401</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4632,6 +4827,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126060437</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4729,6 +4929,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126059336</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4826,6 +5031,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126059586</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -4927,6 +5137,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2024 Fågelsjö</t>
         </is>
       </c>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123771733</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5024,8 +5239,58 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126059838</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>